--- a/src/main/resources/espacios/0 Step/0 - Basic Sentence.xlsx
+++ b/src/main/resources/espacios/0 Step/0 - Basic Sentence.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="1 Basic" sheetId="1" state="visible" r:id="rId3"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3150" uniqueCount="2027">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3142" uniqueCount="2027">
   <si>
     <t xml:space="preserve">talking about time</t>
   </si>
@@ -6618,7 +6618,7 @@
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6629,7 +6629,7 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6695,7 +6695,7 @@
       <c r="B9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       <c r="B10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
       <c r="B11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6728,7 +6728,7 @@
       <c r="B12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6739,7 +6739,7 @@
       <c r="B13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6750,7 +6750,7 @@
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6761,7 +6761,7 @@
       <c r="B15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6783,7 +6783,7 @@
       <c r="B17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6794,7 +6794,7 @@
       <c r="B18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6805,7 +6805,7 @@
       <c r="B19" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       <c r="B21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       <c r="B22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6846,7 +6846,7 @@
       <c r="B23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       <c r="B24" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6868,7 +6868,7 @@
       <c r="B25" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       <c r="B26" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       <c r="B27" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6901,7 +6901,7 @@
       <c r="B28" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       <c r="B29" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6923,7 +6923,7 @@
       <c r="B30" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       <c r="B31" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6945,7 +6945,7 @@
       <c r="B32" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       <c r="B33" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="F33" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6967,7 +6967,7 @@
       <c r="B34" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       <c r="B35" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6989,7 +6989,7 @@
       <c r="B36" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7000,7 +7000,7 @@
       <c r="B37" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7011,7 +7011,7 @@
       <c r="B38" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       <c r="B39" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7041,7 +7041,7 @@
       <c r="B41" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7052,7 +7052,7 @@
       <c r="B42" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       <c r="B43" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="F43" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       <c r="B44" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7085,7 +7085,7 @@
       <c r="B45" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       <c r="B46" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       <c r="B47" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="F47" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       <c r="B48" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       <c r="B49" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F49" s="0" t="s">
+      <c r="F49" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7140,7 +7140,7 @@
       <c r="B50" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
       <c r="B51" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       <c r="B52" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="F52" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7173,7 +7173,7 @@
       <c r="B53" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F53" s="0" t="s">
+      <c r="F53" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
       <c r="B54" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="F54" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7195,7 +7195,7 @@
       <c r="B55" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F55" s="0" t="s">
+      <c r="F55" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       <c r="B56" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F56" s="0" t="s">
+      <c r="F56" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7217,7 +7217,7 @@
       <c r="B57" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F57" s="0" t="s">
+      <c r="F57" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7228,7 +7228,7 @@
       <c r="B58" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="F58" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       <c r="B59" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F59" s="0" t="s">
+      <c r="F59" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       <c r="B61" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F61" s="0" t="s">
+      <c r="F61" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       <c r="B62" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F62" s="0" t="s">
+      <c r="F62" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7280,7 +7280,7 @@
       <c r="B63" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F63" s="0" t="s">
+      <c r="F63" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
       <c r="B64" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F64" s="0" t="s">
+      <c r="F64" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       <c r="B65" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F65" s="0" t="s">
+      <c r="F65" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       <c r="B66" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="F66" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7324,7 +7324,7 @@
       <c r="B67" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F67" s="0" t="s">
+      <c r="F67" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       <c r="B68" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="F68" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       <c r="B69" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F69" s="0" t="s">
+      <c r="F69" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       <c r="B70" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F70" s="0" t="s">
+      <c r="F70" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7368,7 +7368,7 @@
       <c r="B71" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F71" s="0" t="s">
+      <c r="F71" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       <c r="B72" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F72" s="0" t="s">
+      <c r="F72" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
       <c r="B73" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F73" s="0" t="s">
+      <c r="F73" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       <c r="B74" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="F74" s="0" t="s">
+      <c r="F74" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       <c r="B75" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F75" s="0" t="s">
+      <c r="F75" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7423,7 +7423,7 @@
       <c r="B76" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F76" s="0" t="s">
+      <c r="F76" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       <c r="B77" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F77" s="0" t="s">
+      <c r="F77" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       <c r="B78" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="F78" s="0" t="s">
+      <c r="F78" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       <c r="B79" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="F79" s="0" t="s">
+      <c r="F79" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7475,7 +7475,7 @@
       <c r="B81" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="F81" s="0" t="s">
+      <c r="F81" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       <c r="B82" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F82" s="0" t="s">
+      <c r="F82" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7497,7 +7497,7 @@
       <c r="B83" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F83" s="0" t="s">
+      <c r="F83" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       <c r="B84" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F84" s="0" t="s">
+      <c r="F84" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7519,7 +7519,7 @@
       <c r="B85" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F85" s="0" t="s">
+      <c r="F85" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       <c r="B86" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F86" s="0" t="s">
+      <c r="F86" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7541,7 +7541,7 @@
       <c r="B87" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F87" s="0" t="s">
+      <c r="F87" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7552,7 +7552,7 @@
       <c r="B88" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="F88" s="0" t="s">
+      <c r="F88" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7587,9 +7587,7 @@
       <c r="B1" s="1" t="s">
         <v>1748</v>
       </c>
-      <c r="F1" s="0" t="s">
-        <v>4</v>
-      </c>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -7598,7 +7596,7 @@
       <c r="B2" s="1" t="s">
         <v>1750</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7609,7 +7607,7 @@
       <c r="B3" s="1" t="s">
         <v>1752</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7620,7 +7618,7 @@
       <c r="B4" s="1" t="s">
         <v>1754</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7631,7 +7629,7 @@
       <c r="B5" s="1" t="s">
         <v>1756</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7642,7 +7640,7 @@
       <c r="B6" s="1" t="s">
         <v>1758</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7653,7 +7651,7 @@
       <c r="B7" s="1" t="s">
         <v>1760</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7664,7 +7662,7 @@
       <c r="B8" s="1" t="s">
         <v>1762</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7675,7 +7673,7 @@
       <c r="B9" s="1" t="s">
         <v>1764</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7686,7 +7684,7 @@
       <c r="B10" s="1" t="s">
         <v>1766</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7697,7 +7695,7 @@
       <c r="B11" s="1" t="s">
         <v>1768</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7708,7 +7706,7 @@
       <c r="B12" s="1" t="s">
         <v>1770</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7719,7 +7717,7 @@
       <c r="B13" s="1" t="s">
         <v>1772</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7730,7 +7728,7 @@
       <c r="B14" s="1" t="s">
         <v>1774</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7741,7 +7739,7 @@
       <c r="B15" s="1" t="s">
         <v>1776</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7752,7 +7750,7 @@
       <c r="B16" s="1" t="s">
         <v>1778</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7763,7 +7761,7 @@
       <c r="B17" s="1" t="s">
         <v>1780</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7774,7 +7772,7 @@
       <c r="B18" s="1" t="s">
         <v>1782</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7785,7 +7783,7 @@
       <c r="B19" s="1" t="s">
         <v>1784</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7796,7 +7794,7 @@
       <c r="B20" s="1" t="s">
         <v>1786</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7807,7 +7805,7 @@
       <c r="B21" s="1" t="s">
         <v>1788</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7826,7 +7824,7 @@
       <c r="B23" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7837,7 +7835,7 @@
       <c r="B24" s="1" t="s">
         <v>1792</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7848,7 +7846,7 @@
       <c r="B25" s="1" t="s">
         <v>1794</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7859,7 +7857,7 @@
       <c r="B26" s="1" t="s">
         <v>1796</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7870,7 +7868,7 @@
       <c r="B27" s="1" t="s">
         <v>1798</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7881,7 +7879,7 @@
       <c r="B28" s="1" t="s">
         <v>1800</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7892,7 +7890,7 @@
       <c r="B29" s="1" t="s">
         <v>1802</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7903,7 +7901,7 @@
       <c r="B30" s="1" t="s">
         <v>870</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7914,7 +7912,7 @@
       <c r="B31" s="1" t="s">
         <v>1804</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7925,7 +7923,7 @@
       <c r="B32" s="1" t="s">
         <v>1806</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7936,7 +7934,7 @@
       <c r="B33" s="1" t="s">
         <v>1808</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="F33" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7947,7 +7945,7 @@
       <c r="B34" s="1" t="s">
         <v>1810</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7958,7 +7956,7 @@
       <c r="B35" s="1" t="s">
         <v>1812</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7969,7 +7967,7 @@
       <c r="B36" s="1" t="s">
         <v>1814</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7988,7 +7986,7 @@
       <c r="B38" s="1" t="s">
         <v>1818</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7999,7 +7997,7 @@
       <c r="B39" s="1" t="s">
         <v>1820</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8010,7 +8008,7 @@
       <c r="B40" s="1" t="s">
         <v>1822</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8021,7 +8019,7 @@
       <c r="B41" s="1" t="s">
         <v>1824</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8032,7 +8030,7 @@
       <c r="B42" s="1" t="s">
         <v>1826</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8043,7 +8041,7 @@
       <c r="B43" s="1" t="s">
         <v>1828</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="F43" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8054,7 +8052,7 @@
       <c r="B44" s="1" t="s">
         <v>1830</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8065,7 +8063,7 @@
       <c r="B45" s="1" t="s">
         <v>1832</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8076,7 +8074,7 @@
       <c r="B46" s="1" t="s">
         <v>1834</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8087,7 +8085,7 @@
       <c r="B47" s="1" t="s">
         <v>1836</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="F47" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8098,7 +8096,7 @@
       <c r="B48" s="1" t="s">
         <v>1838</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8109,7 +8107,7 @@
       <c r="B49" s="1" t="s">
         <v>1840</v>
       </c>
-      <c r="F49" s="0" t="s">
+      <c r="F49" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8120,7 +8118,7 @@
       <c r="B50" s="1" t="s">
         <v>1842</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8131,7 +8129,7 @@
       <c r="B51" s="1" t="s">
         <v>1844</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8142,7 +8140,7 @@
       <c r="B52" s="1" t="s">
         <v>1846</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="F52" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8153,7 +8151,7 @@
       <c r="B53" s="1" t="s">
         <v>1848</v>
       </c>
-      <c r="F53" s="0" t="s">
+      <c r="F53" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8172,7 +8170,7 @@
       <c r="B55" s="1" t="s">
         <v>1852</v>
       </c>
-      <c r="F55" s="0" t="s">
+      <c r="F55" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8183,7 +8181,7 @@
       <c r="B56" s="1" t="s">
         <v>1854</v>
       </c>
-      <c r="F56" s="0" t="s">
+      <c r="F56" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8194,7 +8192,7 @@
       <c r="B57" s="1" t="s">
         <v>1856</v>
       </c>
-      <c r="F57" s="0" t="s">
+      <c r="F57" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8205,7 +8203,7 @@
       <c r="B58" s="1" t="s">
         <v>1858</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="F58" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8216,7 +8214,7 @@
       <c r="B59" s="1" t="s">
         <v>1860</v>
       </c>
-      <c r="F59" s="0" t="s">
+      <c r="F59" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8227,7 +8225,7 @@
       <c r="B60" s="1" t="s">
         <v>1862</v>
       </c>
-      <c r="F60" s="0" t="s">
+      <c r="F60" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8238,7 +8236,7 @@
       <c r="B61" s="1" t="s">
         <v>1864</v>
       </c>
-      <c r="F61" s="0" t="s">
+      <c r="F61" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8249,7 +8247,7 @@
       <c r="B62" s="1" t="s">
         <v>1866</v>
       </c>
-      <c r="F62" s="0" t="s">
+      <c r="F62" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8260,7 +8258,7 @@
       <c r="B63" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="F63" s="0" t="s">
+      <c r="F63" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8271,7 +8269,7 @@
       <c r="B64" s="1" t="s">
         <v>1868</v>
       </c>
-      <c r="F64" s="0" t="s">
+      <c r="F64" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8282,7 +8280,7 @@
       <c r="B65" s="1" t="s">
         <v>1870</v>
       </c>
-      <c r="F65" s="0" t="s">
+      <c r="F65" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8293,7 +8291,7 @@
       <c r="B66" s="1" t="s">
         <v>1872</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="F66" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8304,7 +8302,7 @@
       <c r="B67" s="1" t="s">
         <v>1874</v>
       </c>
-      <c r="F67" s="0" t="s">
+      <c r="F67" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8315,7 +8313,7 @@
       <c r="B68" s="1" t="s">
         <v>1876</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="F68" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8326,7 +8324,7 @@
       <c r="B69" s="1" t="s">
         <v>1878</v>
       </c>
-      <c r="F69" s="0" t="s">
+      <c r="F69" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8361,9 +8359,7 @@
       <c r="B1" s="1" t="s">
         <v>1880</v>
       </c>
-      <c r="F1" s="0" t="s">
-        <v>4</v>
-      </c>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -8372,7 +8368,7 @@
       <c r="B2" s="1" t="s">
         <v>1882</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8383,7 +8379,7 @@
       <c r="B3" s="1" t="s">
         <v>1884</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8394,7 +8390,7 @@
       <c r="B4" s="1" t="s">
         <v>1886</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8405,7 +8401,7 @@
       <c r="B5" s="1" t="s">
         <v>1888</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8416,7 +8412,7 @@
       <c r="B6" s="1" t="s">
         <v>1890</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8427,7 +8423,7 @@
       <c r="B7" s="1" t="s">
         <v>1892</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8438,7 +8434,7 @@
       <c r="B8" s="1" t="s">
         <v>1894</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8449,7 +8445,7 @@
       <c r="B9" s="1" t="s">
         <v>1896</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8460,7 +8456,7 @@
       <c r="B10" s="1" t="s">
         <v>1898</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8479,7 +8475,7 @@
       <c r="B12" s="1" t="s">
         <v>1902</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8490,7 +8486,7 @@
       <c r="B13" s="1" t="s">
         <v>1904</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8501,7 +8497,7 @@
       <c r="B14" s="1" t="s">
         <v>1906</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8512,7 +8508,7 @@
       <c r="B15" s="1" t="s">
         <v>1908</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8523,7 +8519,7 @@
       <c r="B16" s="1" t="s">
         <v>1910</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8534,7 +8530,7 @@
       <c r="B17" s="1" t="s">
         <v>1912</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8545,7 +8541,7 @@
       <c r="B18" s="1" t="s">
         <v>1914</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8556,7 +8552,7 @@
       <c r="B19" s="1" t="s">
         <v>1916</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8567,7 +8563,7 @@
       <c r="B20" s="1" t="s">
         <v>1918</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8578,7 +8574,7 @@
       <c r="B21" s="1" t="s">
         <v>1920</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8589,7 +8585,7 @@
       <c r="B22" s="1" t="s">
         <v>1922</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8600,7 +8596,7 @@
       <c r="B23" s="1" t="s">
         <v>1924</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8611,7 +8607,7 @@
       <c r="B24" s="1" t="s">
         <v>1926</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8622,7 +8618,7 @@
       <c r="B25" s="1" t="s">
         <v>1928</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8641,7 +8637,7 @@
       <c r="B27" s="1" t="s">
         <v>1932</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8652,7 +8648,7 @@
       <c r="B28" s="1" t="s">
         <v>1934</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8663,7 +8659,7 @@
       <c r="B29" s="1" t="s">
         <v>1936</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8674,7 +8670,7 @@
       <c r="B30" s="1" t="s">
         <v>1938</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8685,7 +8681,7 @@
       <c r="B31" s="1" t="s">
         <v>1940</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8696,7 +8692,7 @@
       <c r="B32" s="1" t="s">
         <v>1942</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8707,7 +8703,7 @@
       <c r="B33" s="1" t="s">
         <v>1944</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="F33" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8718,7 +8714,7 @@
       <c r="B34" s="1" t="s">
         <v>1946</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8729,7 +8725,7 @@
       <c r="B35" s="1" t="s">
         <v>1948</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8740,7 +8736,7 @@
       <c r="B36" s="1" t="s">
         <v>1950</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8751,7 +8747,7 @@
       <c r="B37" s="1" t="s">
         <v>1952</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8762,7 +8758,7 @@
       <c r="B38" s="1" t="s">
         <v>1954</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8773,7 +8769,7 @@
       <c r="B39" s="1" t="s">
         <v>1956</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8784,7 +8780,7 @@
       <c r="B40" s="1" t="s">
         <v>1958</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8795,7 +8791,7 @@
       <c r="B41" s="1" t="s">
         <v>1960</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8806,7 +8802,7 @@
       <c r="B42" s="1" t="s">
         <v>1962</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8817,7 +8813,7 @@
       <c r="B43" s="1" t="s">
         <v>1964</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="F43" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8828,7 +8824,7 @@
       <c r="B44" s="1" t="s">
         <v>1966</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8839,7 +8835,7 @@
       <c r="B45" s="1" t="s">
         <v>1968</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8850,7 +8846,7 @@
       <c r="B46" s="1" t="s">
         <v>1970</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8861,7 +8857,7 @@
       <c r="B47" s="1" t="s">
         <v>1972</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="F47" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8872,7 +8868,7 @@
       <c r="B48" s="1" t="s">
         <v>1974</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8883,7 +8879,7 @@
       <c r="B49" s="1" t="s">
         <v>1976</v>
       </c>
-      <c r="F49" s="0" t="s">
+      <c r="F49" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8894,7 +8890,7 @@
       <c r="B50" s="1" t="s">
         <v>1978</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8905,7 +8901,7 @@
       <c r="B51" s="1" t="s">
         <v>1980</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8924,7 +8920,7 @@
       <c r="B53" s="1" t="s">
         <v>1984</v>
       </c>
-      <c r="F53" s="0" t="s">
+      <c r="F53" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8935,7 +8931,7 @@
       <c r="B54" s="1" t="s">
         <v>1986</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="F54" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8946,7 +8942,7 @@
       <c r="B55" s="1" t="s">
         <v>1988</v>
       </c>
-      <c r="F55" s="0" t="s">
+      <c r="F55" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8957,7 +8953,7 @@
       <c r="B56" s="1" t="s">
         <v>1990</v>
       </c>
-      <c r="F56" s="0" t="s">
+      <c r="F56" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8968,7 +8964,7 @@
       <c r="B57" s="1" t="s">
         <v>1992</v>
       </c>
-      <c r="F57" s="0" t="s">
+      <c r="F57" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8979,7 +8975,7 @@
       <c r="B58" s="1" t="s">
         <v>1994</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="F58" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8990,7 +8986,7 @@
       <c r="B59" s="1" t="s">
         <v>1996</v>
       </c>
-      <c r="F59" s="0" t="s">
+      <c r="F59" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9001,7 +8997,7 @@
       <c r="B60" s="1" t="s">
         <v>1998</v>
       </c>
-      <c r="F60" s="0" t="s">
+      <c r="F60" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9012,7 +9008,7 @@
       <c r="B61" s="1" t="s">
         <v>2000</v>
       </c>
-      <c r="F61" s="0" t="s">
+      <c r="F61" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9023,7 +9019,7 @@
       <c r="B62" s="1" t="s">
         <v>2002</v>
       </c>
-      <c r="F62" s="0" t="s">
+      <c r="F62" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9034,7 +9030,7 @@
       <c r="B63" s="1" t="s">
         <v>2004</v>
       </c>
-      <c r="F63" s="0" t="s">
+      <c r="F63" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9045,7 +9041,7 @@
       <c r="B64" s="1" t="s">
         <v>2006</v>
       </c>
-      <c r="F64" s="0" t="s">
+      <c r="F64" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9056,7 +9052,7 @@
       <c r="B65" s="1" t="s">
         <v>2008</v>
       </c>
-      <c r="F65" s="0" t="s">
+      <c r="F65" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9067,7 +9063,7 @@
       <c r="B66" s="1" t="s">
         <v>2010</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="F66" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9078,7 +9074,7 @@
       <c r="B67" s="1" t="s">
         <v>2012</v>
       </c>
-      <c r="F67" s="0" t="s">
+      <c r="F67" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9089,7 +9085,7 @@
       <c r="B68" s="1" t="s">
         <v>2014</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="F68" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9100,7 +9096,7 @@
       <c r="B69" s="1" t="s">
         <v>2016</v>
       </c>
-      <c r="F69" s="0" t="s">
+      <c r="F69" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9111,7 +9107,7 @@
       <c r="B70" s="1" t="s">
         <v>2018</v>
       </c>
-      <c r="F70" s="0" t="s">
+      <c r="F70" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9122,7 +9118,7 @@
       <c r="B71" s="1" t="s">
         <v>2020</v>
       </c>
-      <c r="F71" s="0" t="s">
+      <c r="F71" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9133,7 +9129,7 @@
       <c r="B72" s="1" t="s">
         <v>2022</v>
       </c>
-      <c r="F72" s="0" t="s">
+      <c r="F72" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9144,7 +9140,7 @@
       <c r="B73" s="1" t="s">
         <v>2024</v>
       </c>
-      <c r="F73" s="0" t="s">
+      <c r="F73" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9155,7 +9151,7 @@
       <c r="B74" s="1" t="s">
         <v>2026</v>
       </c>
-      <c r="F74" s="0" t="s">
+      <c r="F74" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9190,9 +9186,7 @@
       <c r="B1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F1" s="0" t="s">
-        <v>4</v>
-      </c>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -9201,7 +9195,7 @@
       <c r="B2" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9212,7 +9206,7 @@
       <c r="B3" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9223,7 +9217,7 @@
       <c r="B4" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9234,7 +9228,7 @@
       <c r="B5" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9245,7 +9239,7 @@
       <c r="B6" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9256,7 +9250,7 @@
       <c r="B7" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9267,7 +9261,7 @@
       <c r="B8" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9278,7 +9272,7 @@
       <c r="B9" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9289,7 +9283,7 @@
       <c r="B10" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9300,7 +9294,7 @@
       <c r="B11" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9311,7 +9305,7 @@
       <c r="B12" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9322,7 +9316,7 @@
       <c r="B13" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9333,7 +9327,7 @@
       <c r="B14" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9344,7 +9338,7 @@
       <c r="B15" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9355,7 +9349,7 @@
       <c r="B16" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9366,7 +9360,7 @@
       <c r="B17" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9377,7 +9371,7 @@
       <c r="B18" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9388,7 +9382,7 @@
       <c r="B19" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9399,7 +9393,7 @@
       <c r="B20" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9410,7 +9404,7 @@
       <c r="B21" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9421,7 +9415,7 @@
       <c r="B22" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9432,7 +9426,7 @@
       <c r="B23" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9443,7 +9437,7 @@
       <c r="B24" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9454,7 +9448,7 @@
       <c r="B25" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9465,7 +9459,7 @@
       <c r="B26" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9476,7 +9470,7 @@
       <c r="B27" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9495,7 +9489,7 @@
       <c r="B29" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9506,7 +9500,7 @@
       <c r="B30" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9517,7 +9511,7 @@
       <c r="B31" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9528,7 +9522,7 @@
       <c r="B32" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9539,7 +9533,7 @@
       <c r="B33" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="F33" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9550,7 +9544,7 @@
       <c r="B34" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9561,7 +9555,7 @@
       <c r="B35" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9572,7 +9566,7 @@
       <c r="B36" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9583,7 +9577,7 @@
       <c r="B37" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9594,7 +9588,7 @@
       <c r="B38" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9605,7 +9599,7 @@
       <c r="B39" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9616,7 +9610,7 @@
       <c r="B40" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9627,7 +9621,7 @@
       <c r="B41" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9638,7 +9632,7 @@
       <c r="B42" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9649,7 +9643,7 @@
       <c r="B43" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="F43" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9660,7 +9654,7 @@
       <c r="B44" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9671,7 +9665,7 @@
       <c r="B45" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9682,7 +9676,7 @@
       <c r="B46" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9693,7 +9687,7 @@
       <c r="B47" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="F47" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9704,7 +9698,7 @@
       <c r="B48" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9723,7 +9717,7 @@
       <c r="B50" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9734,7 +9728,7 @@
       <c r="B51" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9745,7 +9739,7 @@
       <c r="B52" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="F52" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9756,7 +9750,7 @@
       <c r="B53" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="F53" s="0" t="s">
+      <c r="F53" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9767,7 +9761,7 @@
       <c r="B54" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="F54" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9778,7 +9772,7 @@
       <c r="B55" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="F55" s="0" t="s">
+      <c r="F55" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9789,7 +9783,7 @@
       <c r="B56" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="F56" s="0" t="s">
+      <c r="F56" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9800,7 +9794,7 @@
       <c r="B57" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="F57" s="0" t="s">
+      <c r="F57" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9811,7 +9805,7 @@
       <c r="B58" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="F58" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9822,7 +9816,7 @@
       <c r="B59" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="F59" s="0" t="s">
+      <c r="F59" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9833,7 +9827,7 @@
       <c r="B60" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="F60" s="0" t="s">
+      <c r="F60" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9844,7 +9838,7 @@
       <c r="B61" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="F61" s="0" t="s">
+      <c r="F61" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9855,7 +9849,7 @@
       <c r="B62" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="F62" s="0" t="s">
+      <c r="F62" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9866,7 +9860,7 @@
       <c r="B63" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="F63" s="0" t="s">
+      <c r="F63" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9877,7 +9871,7 @@
       <c r="B64" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="F64" s="0" t="s">
+      <c r="F64" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9888,7 +9882,7 @@
       <c r="B65" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="F65" s="0" t="s">
+      <c r="F65" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9899,7 +9893,7 @@
       <c r="B66" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="F66" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9910,7 +9904,7 @@
       <c r="B67" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="F67" s="0" t="s">
+      <c r="F67" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9921,7 +9915,7 @@
       <c r="B68" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="F68" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9932,7 +9926,7 @@
       <c r="B69" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="F69" s="0" t="s">
+      <c r="F69" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9943,7 +9937,7 @@
       <c r="B70" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="F70" s="0" t="s">
+      <c r="F70" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9954,7 +9948,7 @@
       <c r="B71" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F71" s="0" t="s">
+      <c r="F71" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9965,7 +9959,7 @@
       <c r="B72" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="F72" s="0" t="s">
+      <c r="F72" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9976,7 +9970,7 @@
       <c r="B73" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="F73" s="0" t="s">
+      <c r="F73" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9987,7 +9981,7 @@
       <c r="B74" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="F74" s="0" t="s">
+      <c r="F74" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10006,7 +10000,7 @@
       <c r="B76" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="F76" s="0" t="s">
+      <c r="F76" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10017,7 +10011,7 @@
       <c r="B77" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="F77" s="0" t="s">
+      <c r="F77" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10028,7 +10022,7 @@
       <c r="B78" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="F78" s="0" t="s">
+      <c r="F78" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10039,7 +10033,7 @@
       <c r="B79" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F79" s="0" t="s">
+      <c r="F79" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10050,7 +10044,7 @@
       <c r="B80" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="F80" s="0" t="s">
+      <c r="F80" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10061,7 +10055,7 @@
       <c r="B81" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="F81" s="0" t="s">
+      <c r="F81" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10072,7 +10066,7 @@
       <c r="B82" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="F82" s="0" t="s">
+      <c r="F82" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10083,7 +10077,7 @@
       <c r="B83" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="F83" s="0" t="s">
+      <c r="F83" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10094,7 +10088,7 @@
       <c r="B84" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="F84" s="0" t="s">
+      <c r="F84" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10105,7 +10099,7 @@
       <c r="B85" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="F85" s="0" t="s">
+      <c r="F85" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10116,7 +10110,7 @@
       <c r="B86" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="F86" s="0" t="s">
+      <c r="F86" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10127,7 +10121,7 @@
       <c r="B87" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="F87" s="0" t="s">
+      <c r="F87" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10138,7 +10132,7 @@
       <c r="B88" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="F88" s="0" t="s">
+      <c r="F88" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10149,7 +10143,7 @@
       <c r="B89" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="F89" s="0" t="s">
+      <c r="F89" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10160,7 +10154,7 @@
       <c r="B90" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="F90" s="0" t="s">
+      <c r="F90" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10171,7 +10165,7 @@
       <c r="B91" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="F91" s="0" t="s">
+      <c r="F91" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10182,7 +10176,7 @@
       <c r="B92" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="F92" s="0" t="s">
+      <c r="F92" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10193,7 +10187,7 @@
       <c r="B93" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="F93" s="0" t="s">
+      <c r="F93" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10204,7 +10198,7 @@
       <c r="B94" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="F94" s="0" t="s">
+      <c r="F94" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10215,7 +10209,7 @@
       <c r="B95" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="F95" s="0" t="s">
+      <c r="F95" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10250,9 +10244,7 @@
       <c r="B1" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="F1" s="0" t="s">
-        <v>4</v>
-      </c>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -10261,7 +10253,7 @@
       <c r="B2" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10272,7 +10264,7 @@
       <c r="B3" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10283,7 +10275,7 @@
       <c r="B4" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10294,7 +10286,7 @@
       <c r="B5" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10305,7 +10297,7 @@
       <c r="B6" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10316,7 +10308,7 @@
       <c r="B7" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10327,7 +10319,7 @@
       <c r="B8" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10338,7 +10330,7 @@
       <c r="B9" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10349,7 +10341,7 @@
       <c r="B10" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10360,7 +10352,7 @@
       <c r="B11" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10371,7 +10363,7 @@
       <c r="B12" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10382,7 +10374,7 @@
       <c r="B13" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10393,7 +10385,7 @@
       <c r="B14" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10404,7 +10396,7 @@
       <c r="B15" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10415,7 +10407,7 @@
       <c r="B16" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10426,7 +10418,7 @@
       <c r="B17" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10437,7 +10429,7 @@
       <c r="B18" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10448,7 +10440,7 @@
       <c r="B19" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10459,7 +10451,7 @@
       <c r="B20" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10470,7 +10462,7 @@
       <c r="B21" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10481,7 +10473,7 @@
       <c r="B22" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10492,7 +10484,7 @@
       <c r="B23" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10503,7 +10495,7 @@
       <c r="B24" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10514,7 +10506,7 @@
       <c r="B25" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10525,7 +10517,7 @@
       <c r="B26" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10536,7 +10528,7 @@
       <c r="B27" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10547,7 +10539,7 @@
       <c r="B28" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10558,7 +10550,7 @@
       <c r="B29" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10569,7 +10561,7 @@
       <c r="B30" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10580,7 +10572,7 @@
       <c r="B31" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10599,7 +10591,7 @@
       <c r="B33" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="F33" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10610,7 +10602,7 @@
       <c r="B34" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10621,7 +10613,7 @@
       <c r="B35" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10632,7 +10624,7 @@
       <c r="B36" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10643,7 +10635,7 @@
       <c r="B37" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10654,7 +10646,7 @@
       <c r="B38" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10665,7 +10657,7 @@
       <c r="B39" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10676,7 +10668,7 @@
       <c r="B40" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10687,7 +10679,7 @@
       <c r="B41" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10698,7 +10690,7 @@
       <c r="B42" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10709,7 +10701,7 @@
       <c r="B43" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="F43" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10720,7 +10712,7 @@
       <c r="B44" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10731,7 +10723,7 @@
       <c r="B45" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10742,7 +10734,7 @@
       <c r="B46" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10753,7 +10745,7 @@
       <c r="B47" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="F47" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10764,7 +10756,7 @@
       <c r="B48" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10775,7 +10767,7 @@
       <c r="B49" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="F49" s="0" t="s">
+      <c r="F49" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10786,7 +10778,7 @@
       <c r="B50" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10797,7 +10789,7 @@
       <c r="B51" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10808,7 +10800,7 @@
       <c r="B52" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="F52" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10819,7 +10811,7 @@
       <c r="B53" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="F53" s="0" t="s">
+      <c r="F53" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10830,7 +10822,7 @@
       <c r="B54" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="F54" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10849,7 +10841,7 @@
       <c r="B56" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="F56" s="0" t="s">
+      <c r="F56" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10860,7 +10852,7 @@
       <c r="B57" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="F57" s="0" t="s">
+      <c r="F57" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10871,7 +10863,7 @@
       <c r="B58" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="F58" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10882,7 +10874,7 @@
       <c r="B59" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="F59" s="0" t="s">
+      <c r="F59" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10893,7 +10885,7 @@
       <c r="B60" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="F60" s="0" t="s">
+      <c r="F60" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10904,7 +10896,7 @@
       <c r="B61" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="F61" s="0" t="s">
+      <c r="F61" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10915,7 +10907,7 @@
       <c r="B62" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="F62" s="0" t="s">
+      <c r="F62" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10926,7 +10918,7 @@
       <c r="B63" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="F63" s="0" t="s">
+      <c r="F63" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10937,7 +10929,7 @@
       <c r="B64" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="F64" s="0" t="s">
+      <c r="F64" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10948,7 +10940,7 @@
       <c r="B65" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="F65" s="0" t="s">
+      <c r="F65" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10959,7 +10951,7 @@
       <c r="B66" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="F66" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10970,7 +10962,7 @@
       <c r="B67" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="F67" s="0" t="s">
+      <c r="F67" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10981,7 +10973,7 @@
       <c r="B68" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="F68" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10992,7 +10984,7 @@
       <c r="B69" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="F69" s="0" t="s">
+      <c r="F69" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11003,7 +10995,7 @@
       <c r="B70" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="F70" s="0" t="s">
+      <c r="F70" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11014,7 +11006,7 @@
       <c r="B71" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="F71" s="0" t="s">
+      <c r="F71" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11025,7 +11017,7 @@
       <c r="B72" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="F72" s="0" t="s">
+      <c r="F72" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11036,7 +11028,7 @@
       <c r="B73" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="F73" s="0" t="s">
+      <c r="F73" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11047,7 +11039,7 @@
       <c r="B74" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="F74" s="0" t="s">
+      <c r="F74" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11058,7 +11050,7 @@
       <c r="B75" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="F75" s="0" t="s">
+      <c r="F75" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11069,7 +11061,7 @@
       <c r="B76" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="F76" s="0" t="s">
+      <c r="F76" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11080,7 +11072,7 @@
       <c r="B77" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="F77" s="0" t="s">
+      <c r="F77" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11091,7 +11083,7 @@
       <c r="B78" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="F78" s="0" t="s">
+      <c r="F78" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11102,7 +11094,7 @@
       <c r="B79" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="F79" s="0" t="s">
+      <c r="F79" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11113,7 +11105,7 @@
       <c r="B80" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="F80" s="0" t="s">
+      <c r="F80" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11132,7 +11124,7 @@
       <c r="B82" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="F82" s="0" t="s">
+      <c r="F82" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11143,7 +11135,7 @@
       <c r="B83" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="F83" s="0" t="s">
+      <c r="F83" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11154,7 +11146,7 @@
       <c r="B84" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="F84" s="0" t="s">
+      <c r="F84" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11165,7 +11157,7 @@
       <c r="B85" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="F85" s="0" t="s">
+      <c r="F85" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11176,7 +11168,7 @@
       <c r="B86" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="F86" s="0" t="s">
+      <c r="F86" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11187,7 +11179,7 @@
       <c r="B87" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="F87" s="0" t="s">
+      <c r="F87" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11198,7 +11190,7 @@
       <c r="B88" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="F88" s="0" t="s">
+      <c r="F88" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11209,7 +11201,7 @@
       <c r="B89" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="F89" s="0" t="s">
+      <c r="F89" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11220,7 +11212,7 @@
       <c r="B90" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="F90" s="0" t="s">
+      <c r="F90" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11231,7 +11223,7 @@
       <c r="B91" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="F91" s="0" t="s">
+      <c r="F91" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11242,7 +11234,7 @@
       <c r="B92" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="F92" s="0" t="s">
+      <c r="F92" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11253,7 +11245,7 @@
       <c r="B93" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="F93" s="0" t="s">
+      <c r="F93" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11264,7 +11256,7 @@
       <c r="B94" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="F94" s="0" t="s">
+      <c r="F94" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11275,7 +11267,7 @@
       <c r="B95" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="F95" s="0" t="s">
+      <c r="F95" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11286,7 +11278,7 @@
       <c r="B96" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="F96" s="0" t="s">
+      <c r="F96" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11297,7 +11289,7 @@
       <c r="B97" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="F97" s="0" t="s">
+      <c r="F97" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11308,7 +11300,7 @@
       <c r="B98" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="F98" s="0" t="s">
+      <c r="F98" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11319,7 +11311,7 @@
       <c r="B99" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="F99" s="0" t="s">
+      <c r="F99" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11330,7 +11322,7 @@
       <c r="B100" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="F100" s="0" t="s">
+      <c r="F100" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11341,7 +11333,7 @@
       <c r="B101" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="F101" s="0" t="s">
+      <c r="F101" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11352,7 +11344,7 @@
       <c r="B102" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="F102" s="0" t="s">
+      <c r="F102" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11363,7 +11355,7 @@
       <c r="B103" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="F103" s="0" t="s">
+      <c r="F103" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11374,7 +11366,7 @@
       <c r="B104" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F104" s="0" t="s">
+      <c r="F104" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11385,7 +11377,7 @@
       <c r="B105" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="F105" s="0" t="s">
+      <c r="F105" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11396,7 +11388,7 @@
       <c r="B106" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="F106" s="0" t="s">
+      <c r="F106" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11407,7 +11399,7 @@
       <c r="B107" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="F107" s="0" t="s">
+      <c r="F107" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11418,7 +11410,7 @@
       <c r="B108" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="F108" s="0" t="s">
+      <c r="F108" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11429,7 +11421,7 @@
       <c r="B109" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="F109" s="0" t="s">
+      <c r="F109" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11440,7 +11432,7 @@
       <c r="B110" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="F110" s="0" t="s">
+      <c r="F110" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11451,7 +11443,7 @@
       <c r="B111" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="F111" s="0" t="s">
+      <c r="F111" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11462,7 +11454,7 @@
       <c r="B112" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="F112" s="0" t="s">
+      <c r="F112" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11473,7 +11465,7 @@
       <c r="B113" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="F113" s="0" t="s">
+      <c r="F113" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11484,7 +11476,7 @@
       <c r="B114" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="F114" s="0" t="s">
+      <c r="F114" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11495,7 +11487,7 @@
       <c r="B115" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="F115" s="0" t="s">
+      <c r="F115" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11506,7 +11498,7 @@
       <c r="B116" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="F116" s="0" t="s">
+      <c r="F116" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11517,7 +11509,7 @@
       <c r="B117" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="F117" s="0" t="s">
+      <c r="F117" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11528,7 +11520,7 @@
       <c r="B118" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="F118" s="0" t="s">
+      <c r="F118" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11539,7 +11531,7 @@
       <c r="B119" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="F119" s="0" t="s">
+      <c r="F119" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11550,7 +11542,7 @@
       <c r="B120" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="F120" s="0" t="s">
+      <c r="F120" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11561,7 +11553,7 @@
       <c r="B121" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="F121" s="0" t="s">
+      <c r="F121" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11605,7 +11597,7 @@
       <c r="B2" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11616,7 +11608,7 @@
       <c r="B3" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11627,7 +11619,7 @@
       <c r="B4" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11638,7 +11630,7 @@
       <c r="B5" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11649,7 +11641,7 @@
       <c r="B6" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11660,7 +11652,7 @@
       <c r="B7" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11671,7 +11663,7 @@
       <c r="B8" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11682,7 +11674,7 @@
       <c r="B9" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11693,7 +11685,7 @@
       <c r="B10" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11704,7 +11696,7 @@
       <c r="B11" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11715,7 +11707,7 @@
       <c r="B12" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11726,7 +11718,7 @@
       <c r="B13" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11737,7 +11729,7 @@
       <c r="B14" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11748,7 +11740,7 @@
       <c r="B15" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11759,7 +11751,7 @@
       <c r="B16" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11770,7 +11762,7 @@
       <c r="B17" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11781,7 +11773,7 @@
       <c r="B18" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11792,7 +11784,7 @@
       <c r="B19" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11803,7 +11795,7 @@
       <c r="B20" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11814,7 +11806,7 @@
       <c r="B21" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11825,7 +11817,7 @@
       <c r="B22" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11836,7 +11828,7 @@
       <c r="B23" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11847,7 +11839,7 @@
       <c r="B24" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11858,7 +11850,7 @@
       <c r="B25" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11869,7 +11861,7 @@
       <c r="B26" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11880,7 +11872,7 @@
       <c r="B27" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11891,7 +11883,7 @@
       <c r="B28" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11902,7 +11894,7 @@
       <c r="B29" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11921,7 +11913,7 @@
       <c r="B31" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11932,7 +11924,7 @@
       <c r="B32" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11943,7 +11935,7 @@
       <c r="B33" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="F33" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11954,7 +11946,7 @@
       <c r="B34" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11965,7 +11957,7 @@
       <c r="B35" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11976,7 +11968,7 @@
       <c r="B36" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11987,7 +11979,7 @@
       <c r="B37" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11998,7 +11990,7 @@
       <c r="B38" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12009,7 +12001,7 @@
       <c r="B39" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12020,7 +12012,7 @@
       <c r="B40" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12031,7 +12023,7 @@
       <c r="B41" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12042,7 +12034,7 @@
       <c r="B42" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12053,7 +12045,7 @@
       <c r="B43" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="F43" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12064,7 +12056,7 @@
       <c r="B44" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12075,7 +12067,7 @@
       <c r="B45" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12086,7 +12078,7 @@
       <c r="B46" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12097,7 +12089,7 @@
       <c r="B47" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="F47" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12108,7 +12100,7 @@
       <c r="B48" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12119,7 +12111,7 @@
       <c r="B49" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="F49" s="0" t="s">
+      <c r="F49" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12130,7 +12122,7 @@
       <c r="B50" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12141,7 +12133,7 @@
       <c r="B51" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12152,7 +12144,7 @@
       <c r="B52" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="F52" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12163,7 +12155,7 @@
       <c r="B53" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="F53" s="0" t="s">
+      <c r="F53" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12174,7 +12166,7 @@
       <c r="B54" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="F54" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12185,7 +12177,7 @@
       <c r="B55" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="F55" s="0" t="s">
+      <c r="F55" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12196,7 +12188,7 @@
       <c r="B56" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="F56" s="0" t="s">
+      <c r="F56" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12207,7 +12199,7 @@
       <c r="B57" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="F57" s="0" t="s">
+      <c r="F57" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12218,7 +12210,7 @@
       <c r="B58" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="F58" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12237,7 +12229,7 @@
       <c r="B60" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="F60" s="0" t="s">
+      <c r="F60" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12248,7 +12240,7 @@
       <c r="B61" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="F61" s="0" t="s">
+      <c r="F61" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12259,7 +12251,7 @@
       <c r="B62" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="F62" s="0" t="s">
+      <c r="F62" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12270,7 +12262,7 @@
       <c r="B63" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="F63" s="0" t="s">
+      <c r="F63" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12281,7 +12273,7 @@
       <c r="B64" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="F64" s="0" t="s">
+      <c r="F64" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12292,7 +12284,7 @@
       <c r="B65" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="F65" s="0" t="s">
+      <c r="F65" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12303,7 +12295,7 @@
       <c r="B66" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="F66" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12314,7 +12306,7 @@
       <c r="B67" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="F67" s="0" t="s">
+      <c r="F67" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12325,7 +12317,7 @@
       <c r="B68" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="F68" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12336,7 +12328,7 @@
       <c r="B69" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="F69" s="0" t="s">
+      <c r="F69" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12347,7 +12339,7 @@
       <c r="B70" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="F70" s="0" t="s">
+      <c r="F70" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12358,7 +12350,7 @@
       <c r="B71" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="F71" s="0" t="s">
+      <c r="F71" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12369,7 +12361,7 @@
       <c r="B72" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="F72" s="0" t="s">
+      <c r="F72" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12380,7 +12372,7 @@
       <c r="B73" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="F73" s="0" t="s">
+      <c r="F73" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12391,7 +12383,7 @@
       <c r="B74" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="F74" s="0" t="s">
+      <c r="F74" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12402,7 +12394,7 @@
       <c r="B75" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="F75" s="0" t="s">
+      <c r="F75" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12413,7 +12405,7 @@
       <c r="B76" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="F76" s="0" t="s">
+      <c r="F76" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12424,7 +12416,7 @@
       <c r="B77" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="F77" s="0" t="s">
+      <c r="F77" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12435,7 +12427,7 @@
       <c r="B78" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="F78" s="0" t="s">
+      <c r="F78" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12446,7 +12438,7 @@
       <c r="B79" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="F79" s="0" t="s">
+      <c r="F79" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12457,7 +12449,7 @@
       <c r="B80" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="F80" s="0" t="s">
+      <c r="F80" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12468,7 +12460,7 @@
       <c r="B81" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="F81" s="0" t="s">
+      <c r="F81" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12479,7 +12471,7 @@
       <c r="B82" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="F82" s="0" t="s">
+      <c r="F82" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12490,7 +12482,7 @@
       <c r="B83" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="F83" s="0" t="s">
+      <c r="F83" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12501,12 +12493,12 @@
       <c r="B84" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="F84" s="0" t="s">
+      <c r="F84" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F85" s="0" t="s">
+      <c r="F85" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12517,7 +12509,7 @@
       <c r="B86" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="F86" s="0" t="s">
+      <c r="F86" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12528,7 +12520,7 @@
       <c r="B87" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="F87" s="0" t="s">
+      <c r="F87" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12539,7 +12531,7 @@
       <c r="B88" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="F88" s="0" t="s">
+      <c r="F88" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12550,7 +12542,7 @@
       <c r="B89" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="F89" s="0" t="s">
+      <c r="F89" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12561,7 +12553,7 @@
       <c r="B90" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="F90" s="0" t="s">
+      <c r="F90" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12572,7 +12564,7 @@
       <c r="B91" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="F91" s="0" t="s">
+      <c r="F91" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12583,7 +12575,7 @@
       <c r="B92" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="F92" s="0" t="s">
+      <c r="F92" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12594,7 +12586,7 @@
       <c r="B93" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="F93" s="0" t="s">
+      <c r="F93" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12605,7 +12597,7 @@
       <c r="B94" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="F94" s="0" t="s">
+      <c r="F94" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12616,7 +12608,7 @@
       <c r="B95" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="F95" s="0" t="s">
+      <c r="F95" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12627,7 +12619,7 @@
       <c r="B96" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="F96" s="0" t="s">
+      <c r="F96" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12638,7 +12630,7 @@
       <c r="B97" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="F97" s="0" t="s">
+      <c r="F97" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12649,7 +12641,7 @@
       <c r="B98" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="F98" s="0" t="s">
+      <c r="F98" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12660,7 +12652,7 @@
       <c r="B99" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="F99" s="0" t="s">
+      <c r="F99" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12671,7 +12663,7 @@
       <c r="B100" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="F100" s="0" t="s">
+      <c r="F100" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12682,7 +12674,7 @@
       <c r="B101" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="F101" s="0" t="s">
+      <c r="F101" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12693,7 +12685,7 @@
       <c r="B102" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="F102" s="0" t="s">
+      <c r="F102" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12704,7 +12696,7 @@
       <c r="B103" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="F103" s="0" t="s">
+      <c r="F103" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12715,7 +12707,7 @@
       <c r="B104" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="F104" s="0" t="s">
+      <c r="F104" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12726,7 +12718,7 @@
       <c r="B105" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="F105" s="0" t="s">
+      <c r="F105" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12737,7 +12729,7 @@
       <c r="B106" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="F106" s="0" t="s">
+      <c r="F106" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12748,7 +12740,7 @@
       <c r="B107" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="F107" s="0" t="s">
+      <c r="F107" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12759,7 +12751,7 @@
       <c r="B108" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="F108" s="0" t="s">
+      <c r="F108" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12770,7 +12762,7 @@
       <c r="B109" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="F109" s="0" t="s">
+      <c r="F109" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12781,7 +12773,7 @@
       <c r="B110" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="F110" s="0" t="s">
+      <c r="F110" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12792,7 +12784,7 @@
       <c r="B111" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="F111" s="0" t="s">
+      <c r="F111" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12803,7 +12795,7 @@
       <c r="B112" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="F112" s="0" t="s">
+      <c r="F112" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12814,7 +12806,7 @@
       <c r="B113" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F113" s="0" t="s">
+      <c r="F113" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12825,7 +12817,7 @@
       <c r="B114" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="F114" s="0" t="s">
+      <c r="F114" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12836,7 +12828,7 @@
       <c r="B115" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="F115" s="0" t="s">
+      <c r="F115" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12847,7 +12839,7 @@
       <c r="B116" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="F116" s="0" t="s">
+      <c r="F116" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12858,7 +12850,7 @@
       <c r="B117" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="F117" s="0" t="s">
+      <c r="F117" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12869,7 +12861,7 @@
       <c r="B118" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="F118" s="0" t="s">
+      <c r="F118" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12880,7 +12872,7 @@
       <c r="B119" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="F119" s="0" t="s">
+      <c r="F119" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12891,7 +12883,7 @@
       <c r="B120" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="F120" s="0" t="s">
+      <c r="F120" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12926,9 +12918,7 @@
       <c r="B1" s="1" t="s">
         <v>804</v>
       </c>
-      <c r="F1" s="0" t="s">
-        <v>4</v>
-      </c>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -12937,7 +12927,7 @@
       <c r="B2" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12948,7 +12938,7 @@
       <c r="B3" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12959,7 +12949,7 @@
       <c r="B4" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12970,7 +12960,7 @@
       <c r="B5" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12981,7 +12971,7 @@
       <c r="B6" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12992,7 +12982,7 @@
       <c r="B7" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13003,7 +12993,7 @@
       <c r="B8" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13014,7 +13004,7 @@
       <c r="B9" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13025,7 +13015,7 @@
       <c r="B10" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13036,7 +13026,7 @@
       <c r="B11" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13047,7 +13037,7 @@
       <c r="B12" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13058,7 +13048,7 @@
       <c r="B13" s="1" t="s">
         <v>828</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13069,7 +13059,7 @@
       <c r="B14" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13080,7 +13070,7 @@
       <c r="B15" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13091,7 +13081,7 @@
       <c r="B16" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13102,7 +13092,7 @@
       <c r="B17" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13113,7 +13103,7 @@
       <c r="B18" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13124,7 +13114,7 @@
       <c r="B19" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13135,7 +13125,7 @@
       <c r="B20" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13146,7 +13136,7 @@
       <c r="B21" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13157,7 +13147,7 @@
       <c r="B22" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13168,7 +13158,7 @@
       <c r="B23" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13179,7 +13169,7 @@
       <c r="B24" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13190,7 +13180,7 @@
       <c r="B25" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13201,7 +13191,7 @@
       <c r="B26" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13212,7 +13202,7 @@
       <c r="B27" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13231,7 +13221,7 @@
       <c r="B29" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13242,7 +13232,7 @@
       <c r="B30" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13253,7 +13243,7 @@
       <c r="B31" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13264,7 +13254,7 @@
       <c r="B32" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13275,7 +13265,7 @@
       <c r="B33" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="F33" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13286,7 +13276,7 @@
       <c r="B34" s="1" t="s">
         <v>868</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13297,7 +13287,7 @@
       <c r="B35" s="1" t="s">
         <v>870</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13308,7 +13298,7 @@
       <c r="B36" s="1" t="s">
         <v>872</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13319,7 +13309,7 @@
       <c r="B37" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13330,7 +13320,7 @@
       <c r="B38" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13341,7 +13331,7 @@
       <c r="B39" s="1" t="s">
         <v>876</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13352,7 +13342,7 @@
       <c r="B40" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13363,7 +13353,7 @@
       <c r="B41" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13374,7 +13364,7 @@
       <c r="B42" s="1" t="s">
         <v>882</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13385,7 +13375,7 @@
       <c r="B43" s="1" t="s">
         <v>884</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="F43" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13396,7 +13386,7 @@
       <c r="B44" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13407,7 +13397,7 @@
       <c r="B45" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13418,7 +13408,7 @@
       <c r="B46" s="1" t="s">
         <v>888</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13429,7 +13419,7 @@
       <c r="B47" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="F47" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13440,7 +13430,7 @@
       <c r="B48" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13459,7 +13449,7 @@
       <c r="B50" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13470,7 +13460,7 @@
       <c r="B51" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13481,7 +13471,7 @@
       <c r="B52" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="F52" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13492,7 +13482,7 @@
       <c r="B53" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="F53" s="0" t="s">
+      <c r="F53" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13503,7 +13493,7 @@
       <c r="B54" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="F54" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13514,7 +13504,7 @@
       <c r="B55" s="1" t="s">
         <v>906</v>
       </c>
-      <c r="F55" s="0" t="s">
+      <c r="F55" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13525,7 +13515,7 @@
       <c r="B56" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="F56" s="0" t="s">
+      <c r="F56" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13536,7 +13526,7 @@
       <c r="B57" s="1" t="s">
         <v>910</v>
       </c>
-      <c r="F57" s="0" t="s">
+      <c r="F57" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13547,7 +13537,7 @@
       <c r="B58" s="1" t="s">
         <v>912</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="F58" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13558,7 +13548,7 @@
       <c r="B59" s="1" t="s">
         <v>914</v>
       </c>
-      <c r="F59" s="0" t="s">
+      <c r="F59" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13569,7 +13559,7 @@
       <c r="B60" s="1" t="s">
         <v>916</v>
       </c>
-      <c r="F60" s="0" t="s">
+      <c r="F60" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13588,7 +13578,7 @@
       <c r="B62" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="F62" s="0" t="s">
+      <c r="F62" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13599,7 +13589,7 @@
       <c r="B63" s="1" t="s">
         <v>920</v>
       </c>
-      <c r="F63" s="0" t="s">
+      <c r="F63" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13610,7 +13600,7 @@
       <c r="B64" s="1" t="s">
         <v>922</v>
       </c>
-      <c r="F64" s="0" t="s">
+      <c r="F64" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13621,7 +13611,7 @@
       <c r="B65" s="1" t="s">
         <v>924</v>
       </c>
-      <c r="F65" s="0" t="s">
+      <c r="F65" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13632,7 +13622,7 @@
       <c r="B66" s="1" t="s">
         <v>926</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="F66" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13643,7 +13633,7 @@
       <c r="B67" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="F67" s="0" t="s">
+      <c r="F67" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13654,7 +13644,7 @@
       <c r="B68" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="F68" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13665,7 +13655,7 @@
       <c r="B69" s="1" t="s">
         <v>932</v>
       </c>
-      <c r="F69" s="0" t="s">
+      <c r="F69" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13676,7 +13666,7 @@
       <c r="B70" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="F70" s="0" t="s">
+      <c r="F70" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13687,7 +13677,7 @@
       <c r="B71" s="1" t="s">
         <v>936</v>
       </c>
-      <c r="F71" s="0" t="s">
+      <c r="F71" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13698,7 +13688,7 @@
       <c r="B72" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="F72" s="0" t="s">
+      <c r="F72" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13717,7 +13707,7 @@
       <c r="B74" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="F74" s="0" t="s">
+      <c r="F74" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13728,7 +13718,7 @@
       <c r="B75" s="1" t="s">
         <v>944</v>
       </c>
-      <c r="F75" s="0" t="s">
+      <c r="F75" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13739,7 +13729,7 @@
       <c r="B76" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="F76" s="0" t="s">
+      <c r="F76" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13750,7 +13740,7 @@
       <c r="B77" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="F77" s="0" t="s">
+      <c r="F77" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13761,7 +13751,7 @@
       <c r="B78" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="F78" s="0" t="s">
+      <c r="F78" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13796,9 +13786,7 @@
       <c r="B1" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="F1" s="0" t="s">
-        <v>4</v>
-      </c>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -13807,7 +13795,7 @@
       <c r="B2" s="1" t="s">
         <v>954</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13818,7 +13806,7 @@
       <c r="B3" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13829,7 +13817,7 @@
       <c r="B4" s="1" t="s">
         <v>958</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13840,7 +13828,7 @@
       <c r="B5" s="1" t="s">
         <v>960</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13851,7 +13839,7 @@
       <c r="B6" s="1" t="s">
         <v>962</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13862,7 +13850,7 @@
       <c r="B7" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13873,7 +13861,7 @@
       <c r="B8" s="1" t="s">
         <v>966</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13884,7 +13872,7 @@
       <c r="B9" s="1" t="s">
         <v>968</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13895,7 +13883,7 @@
       <c r="B10" s="1" t="s">
         <v>970</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13906,7 +13894,7 @@
       <c r="B11" s="1" t="s">
         <v>972</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13917,7 +13905,7 @@
       <c r="B12" s="1" t="s">
         <v>974</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13936,7 +13924,7 @@
       <c r="B14" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13947,7 +13935,7 @@
       <c r="B15" s="1" t="s">
         <v>980</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13958,7 +13946,7 @@
       <c r="B16" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13969,7 +13957,7 @@
       <c r="B17" s="1" t="s">
         <v>984</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13980,7 +13968,7 @@
       <c r="B18" s="1" t="s">
         <v>986</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -13991,7 +13979,7 @@
       <c r="B19" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14002,7 +13990,7 @@
       <c r="B20" s="1" t="s">
         <v>990</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14013,7 +14001,7 @@
       <c r="B21" s="1" t="s">
         <v>992</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14024,7 +14012,7 @@
       <c r="B22" s="1" t="s">
         <v>994</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14035,7 +14023,7 @@
       <c r="B23" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14046,7 +14034,7 @@
       <c r="B24" s="1" t="s">
         <v>998</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14057,7 +14045,7 @@
       <c r="B25" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14068,7 +14056,7 @@
       <c r="B26" s="1" t="s">
         <v>1002</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14079,7 +14067,7 @@
       <c r="B27" s="1" t="s">
         <v>1004</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14090,7 +14078,7 @@
       <c r="B28" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14101,7 +14089,7 @@
       <c r="B29" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14112,7 +14100,7 @@
       <c r="B30" s="1" t="s">
         <v>1010</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14123,7 +14111,7 @@
       <c r="B31" s="1" t="s">
         <v>1012</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14134,7 +14122,7 @@
       <c r="B32" s="1" t="s">
         <v>1014</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14145,7 +14133,7 @@
       <c r="B33" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="F33" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14156,7 +14144,7 @@
       <c r="B34" s="1" t="s">
         <v>1018</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14167,7 +14155,7 @@
       <c r="B35" s="1" t="s">
         <v>1020</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14186,7 +14174,7 @@
       <c r="B37" s="1" t="s">
         <v>1024</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14197,7 +14185,7 @@
       <c r="B38" s="1" t="s">
         <v>1026</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14208,7 +14196,7 @@
       <c r="B39" s="1" t="s">
         <v>1028</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14219,7 +14207,7 @@
       <c r="B40" s="1" t="s">
         <v>1030</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14230,7 +14218,7 @@
       <c r="B41" s="1" t="s">
         <v>1032</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14241,7 +14229,7 @@
       <c r="B42" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14252,7 +14240,7 @@
       <c r="B43" s="1" t="s">
         <v>1036</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="F43" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14263,7 +14251,7 @@
       <c r="B44" s="1" t="s">
         <v>1038</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14274,7 +14262,7 @@
       <c r="B45" s="1" t="s">
         <v>1040</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14285,7 +14273,7 @@
       <c r="B46" s="1" t="s">
         <v>1042</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14296,7 +14284,7 @@
       <c r="B47" s="1" t="s">
         <v>1044</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="F47" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14307,7 +14295,7 @@
       <c r="B48" s="1" t="s">
         <v>1046</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14318,7 +14306,7 @@
       <c r="B49" s="1" t="s">
         <v>1048</v>
       </c>
-      <c r="F49" s="0" t="s">
+      <c r="F49" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14329,7 +14317,7 @@
       <c r="B50" s="1" t="s">
         <v>1050</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14340,7 +14328,7 @@
       <c r="B51" s="1" t="s">
         <v>1052</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14351,7 +14339,7 @@
       <c r="B52" s="1" t="s">
         <v>1054</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="F52" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14362,7 +14350,7 @@
       <c r="B53" s="1" t="s">
         <v>1056</v>
       </c>
-      <c r="F53" s="0" t="s">
+      <c r="F53" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14373,7 +14361,7 @@
       <c r="B54" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="F54" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14384,7 +14372,7 @@
       <c r="B55" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="F55" s="0" t="s">
+      <c r="F55" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14403,7 +14391,7 @@
       <c r="B57" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="F57" s="0" t="s">
+      <c r="F57" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14414,7 +14402,7 @@
       <c r="B58" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="F58" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14425,7 +14413,7 @@
       <c r="B59" s="1" t="s">
         <v>1066</v>
       </c>
-      <c r="F59" s="0" t="s">
+      <c r="F59" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14436,7 +14424,7 @@
       <c r="B60" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="F60" s="0" t="s">
+      <c r="F60" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14447,7 +14435,7 @@
       <c r="B61" s="1" t="s">
         <v>1070</v>
       </c>
-      <c r="F61" s="0" t="s">
+      <c r="F61" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14458,7 +14446,7 @@
       <c r="B62" s="1" t="s">
         <v>1072</v>
       </c>
-      <c r="F62" s="0" t="s">
+      <c r="F62" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14469,7 +14457,7 @@
       <c r="B63" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="F63" s="0" t="s">
+      <c r="F63" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14480,7 +14468,7 @@
       <c r="B64" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="F64" s="0" t="s">
+      <c r="F64" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14491,7 +14479,7 @@
       <c r="B65" s="1" t="s">
         <v>1078</v>
       </c>
-      <c r="F65" s="0" t="s">
+      <c r="F65" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14502,7 +14490,7 @@
       <c r="B66" s="1" t="s">
         <v>1080</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="F66" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14513,7 +14501,7 @@
       <c r="B67" s="1" t="s">
         <v>1082</v>
       </c>
-      <c r="F67" s="0" t="s">
+      <c r="F67" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14524,7 +14512,7 @@
       <c r="B68" s="1" t="s">
         <v>1084</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="F68" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14535,7 +14523,7 @@
       <c r="B69" s="1" t="s">
         <v>1086</v>
       </c>
-      <c r="F69" s="0" t="s">
+      <c r="F69" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14554,7 +14542,7 @@
       <c r="B71" s="1" t="s">
         <v>1090</v>
       </c>
-      <c r="F71" s="0" t="s">
+      <c r="F71" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14565,7 +14553,7 @@
       <c r="B72" s="1" t="s">
         <v>1092</v>
       </c>
-      <c r="F72" s="0" t="s">
+      <c r="F72" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14576,7 +14564,7 @@
       <c r="B73" s="1" t="s">
         <v>1094</v>
       </c>
-      <c r="F73" s="0" t="s">
+      <c r="F73" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14587,7 +14575,7 @@
       <c r="B74" s="1" t="s">
         <v>1096</v>
       </c>
-      <c r="F74" s="0" t="s">
+      <c r="F74" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14598,7 +14586,7 @@
       <c r="B75" s="1" t="s">
         <v>1098</v>
       </c>
-      <c r="F75" s="0" t="s">
+      <c r="F75" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14609,7 +14597,7 @@
       <c r="B76" s="1" t="s">
         <v>1100</v>
       </c>
-      <c r="F76" s="0" t="s">
+      <c r="F76" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14620,7 +14608,7 @@
       <c r="B77" s="1" t="s">
         <v>1102</v>
       </c>
-      <c r="F77" s="0" t="s">
+      <c r="F77" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14631,7 +14619,7 @@
       <c r="B78" s="1" t="s">
         <v>1104</v>
       </c>
-      <c r="F78" s="0" t="s">
+      <c r="F78" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14642,7 +14630,7 @@
       <c r="B79" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="F79" s="0" t="s">
+      <c r="F79" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14653,7 +14641,7 @@
       <c r="B80" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F80" s="0" t="s">
+      <c r="F80" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14664,7 +14652,7 @@
       <c r="B81" s="1" t="s">
         <v>1109</v>
       </c>
-      <c r="F81" s="0" t="s">
+      <c r="F81" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14675,7 +14663,7 @@
       <c r="B82" s="1" t="s">
         <v>1111</v>
       </c>
-      <c r="F82" s="0" t="s">
+      <c r="F82" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14686,7 +14674,7 @@
       <c r="B83" s="1" t="s">
         <v>1113</v>
       </c>
-      <c r="F83" s="0" t="s">
+      <c r="F83" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14697,7 +14685,7 @@
       <c r="B84" s="1" t="s">
         <v>1115</v>
       </c>
-      <c r="F84" s="0" t="s">
+      <c r="F84" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14716,7 +14704,7 @@
       <c r="B86" s="1" t="s">
         <v>1119</v>
       </c>
-      <c r="F86" s="0" t="s">
+      <c r="F86" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14727,7 +14715,7 @@
       <c r="B87" s="1" t="s">
         <v>1121</v>
       </c>
-      <c r="F87" s="0" t="s">
+      <c r="F87" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14738,7 +14726,7 @@
       <c r="B88" s="1" t="s">
         <v>1123</v>
       </c>
-      <c r="F88" s="0" t="s">
+      <c r="F88" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14749,7 +14737,7 @@
       <c r="B89" s="1" t="s">
         <v>1125</v>
       </c>
-      <c r="F89" s="0" t="s">
+      <c r="F89" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14760,7 +14748,7 @@
       <c r="B90" s="1" t="s">
         <v>1127</v>
       </c>
-      <c r="F90" s="0" t="s">
+      <c r="F90" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14771,7 +14759,7 @@
       <c r="B91" s="1" t="s">
         <v>1129</v>
       </c>
-      <c r="F91" s="0" t="s">
+      <c r="F91" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14782,7 +14770,7 @@
       <c r="B92" s="1" t="s">
         <v>1131</v>
       </c>
-      <c r="F92" s="0" t="s">
+      <c r="F92" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14793,7 +14781,7 @@
       <c r="B93" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="F93" s="0" t="s">
+      <c r="F93" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14804,7 +14792,7 @@
       <c r="B94" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F94" s="0" t="s">
+      <c r="F94" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14815,7 +14803,7 @@
       <c r="B95" s="1" t="s">
         <v>1135</v>
       </c>
-      <c r="F95" s="0" t="s">
+      <c r="F95" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14826,7 +14814,7 @@
       <c r="B96" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="F96" s="0" t="s">
+      <c r="F96" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14837,7 +14825,7 @@
       <c r="B97" s="1" t="s">
         <v>1139</v>
       </c>
-      <c r="F97" s="0" t="s">
+      <c r="F97" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14848,7 +14836,7 @@
       <c r="B98" s="1" t="s">
         <v>1141</v>
       </c>
-      <c r="F98" s="0" t="s">
+      <c r="F98" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14867,7 +14855,7 @@
       <c r="B100" s="1" t="s">
         <v>1145</v>
       </c>
-      <c r="F100" s="0" t="s">
+      <c r="F100" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14878,7 +14866,7 @@
       <c r="B101" s="1" t="s">
         <v>1147</v>
       </c>
-      <c r="F101" s="0" t="s">
+      <c r="F101" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14889,7 +14877,7 @@
       <c r="B102" s="1" t="s">
         <v>1149</v>
       </c>
-      <c r="F102" s="0" t="s">
+      <c r="F102" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14900,7 +14888,7 @@
       <c r="B103" s="1" t="s">
         <v>1151</v>
       </c>
-      <c r="F103" s="0" t="s">
+      <c r="F103" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14911,7 +14899,7 @@
       <c r="B104" s="1" t="s">
         <v>1153</v>
       </c>
-      <c r="F104" s="0" t="s">
+      <c r="F104" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14922,7 +14910,7 @@
       <c r="B105" s="1" t="s">
         <v>1155</v>
       </c>
-      <c r="F105" s="0" t="s">
+      <c r="F105" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14933,7 +14921,7 @@
       <c r="B106" s="1" t="s">
         <v>1157</v>
       </c>
-      <c r="F106" s="0" t="s">
+      <c r="F106" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14944,7 +14932,7 @@
       <c r="B107" s="1" t="s">
         <v>1159</v>
       </c>
-      <c r="F107" s="0" t="s">
+      <c r="F107" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14955,7 +14943,7 @@
       <c r="B108" s="1" t="s">
         <v>1161</v>
       </c>
-      <c r="F108" s="0" t="s">
+      <c r="F108" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14966,7 +14954,7 @@
       <c r="B109" s="1" t="s">
         <v>1163</v>
       </c>
-      <c r="F109" s="0" t="s">
+      <c r="F109" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14977,7 +14965,7 @@
       <c r="B110" s="1" t="s">
         <v>1165</v>
       </c>
-      <c r="F110" s="0" t="s">
+      <c r="F110" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14988,7 +14976,7 @@
       <c r="B111" s="1" t="s">
         <v>1167</v>
       </c>
-      <c r="F111" s="0" t="s">
+      <c r="F111" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -14999,7 +14987,7 @@
       <c r="B112" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="F112" s="0" t="s">
+      <c r="F112" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15010,7 +14998,7 @@
       <c r="B113" s="1" t="s">
         <v>1171</v>
       </c>
-      <c r="F113" s="0" t="s">
+      <c r="F113" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15021,7 +15009,7 @@
       <c r="B114" s="1" t="s">
         <v>1173</v>
       </c>
-      <c r="F114" s="0" t="s">
+      <c r="F114" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15064,7 +15052,7 @@
       <c r="B2" s="1" t="s">
         <v>1177</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15075,7 +15063,7 @@
       <c r="B3" s="1" t="s">
         <v>1179</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15086,7 +15074,7 @@
       <c r="B4" s="1" t="s">
         <v>1181</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15097,7 +15085,7 @@
       <c r="B5" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15108,7 +15096,7 @@
       <c r="B6" s="1" t="s">
         <v>1185</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15119,7 +15107,7 @@
       <c r="B7" s="1" t="s">
         <v>1187</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15130,7 +15118,7 @@
       <c r="B8" s="1" t="s">
         <v>1189</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15141,7 +15129,7 @@
       <c r="B9" s="1" t="s">
         <v>1191</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15152,7 +15140,7 @@
       <c r="B10" s="1" t="s">
         <v>1193</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15163,7 +15151,7 @@
       <c r="B11" s="1" t="s">
         <v>1195</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15174,7 +15162,7 @@
       <c r="B12" s="1" t="s">
         <v>1197</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15185,7 +15173,7 @@
       <c r="B13" s="1" t="s">
         <v>1199</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15196,7 +15184,7 @@
       <c r="B14" s="1" t="s">
         <v>1201</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15207,7 +15195,7 @@
       <c r="B15" s="1" t="s">
         <v>1203</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15218,7 +15206,7 @@
       <c r="B16" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15237,7 +15225,7 @@
       <c r="B18" s="1" t="s">
         <v>1209</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15248,7 +15236,7 @@
       <c r="B19" s="1" t="s">
         <v>1211</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15259,7 +15247,7 @@
       <c r="B20" s="1" t="s">
         <v>1213</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15270,7 +15258,7 @@
       <c r="B21" s="1" t="s">
         <v>1215</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15281,7 +15269,7 @@
       <c r="B22" s="1" t="s">
         <v>1217</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15292,7 +15280,7 @@
       <c r="B23" s="1" t="s">
         <v>1219</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15303,7 +15291,7 @@
       <c r="B24" s="1" t="s">
         <v>1221</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15314,7 +15302,7 @@
       <c r="B25" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15325,7 +15313,7 @@
       <c r="B26" s="1" t="s">
         <v>1225</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15336,7 +15324,7 @@
       <c r="B27" s="1" t="s">
         <v>1227</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15347,7 +15335,7 @@
       <c r="B28" s="1" t="s">
         <v>1229</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15358,7 +15346,7 @@
       <c r="B29" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15369,7 +15357,7 @@
       <c r="B30" s="1" t="s">
         <v>1231</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15380,7 +15368,7 @@
       <c r="B31" s="1" t="s">
         <v>1233</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15391,7 +15379,7 @@
       <c r="B32" s="1" t="s">
         <v>1235</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15402,7 +15390,7 @@
       <c r="B33" s="1" t="s">
         <v>1237</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="F33" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15413,7 +15401,7 @@
       <c r="B34" s="1" t="s">
         <v>1239</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15424,7 +15412,7 @@
       <c r="B35" s="1" t="s">
         <v>1241</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15435,7 +15423,7 @@
       <c r="B36" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15446,7 +15434,7 @@
       <c r="B37" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15465,7 +15453,7 @@
       <c r="B39" s="1" t="s">
         <v>1246</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15476,7 +15464,7 @@
       <c r="B40" s="1" t="s">
         <v>1248</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15487,7 +15475,7 @@
       <c r="B41" s="1" t="s">
         <v>1250</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15498,7 +15486,7 @@
       <c r="B42" s="1" t="s">
         <v>1252</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15509,7 +15497,7 @@
       <c r="B43" s="1" t="s">
         <v>1254</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="F43" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15520,7 +15508,7 @@
       <c r="B44" s="1" t="s">
         <v>1256</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15531,7 +15519,7 @@
       <c r="B45" s="1" t="s">
         <v>1258</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15542,7 +15530,7 @@
       <c r="B46" s="1" t="s">
         <v>1260</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15553,7 +15541,7 @@
       <c r="B47" s="1" t="s">
         <v>1262</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="F47" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15564,7 +15552,7 @@
       <c r="B48" s="1" t="s">
         <v>1264</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15575,7 +15563,7 @@
       <c r="B49" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="F49" s="0" t="s">
+      <c r="F49" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15586,7 +15574,7 @@
       <c r="B50" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15597,7 +15585,7 @@
       <c r="B51" s="1" t="s">
         <v>1270</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15608,7 +15596,7 @@
       <c r="B52" s="1" t="s">
         <v>1272</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="F52" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15619,7 +15607,7 @@
       <c r="B53" s="1" t="s">
         <v>1274</v>
       </c>
-      <c r="F53" s="0" t="s">
+      <c r="F53" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15630,7 +15618,7 @@
       <c r="B54" s="1" t="s">
         <v>1276</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="F54" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15641,7 +15629,7 @@
       <c r="B55" s="1" t="s">
         <v>1278</v>
       </c>
-      <c r="F55" s="0" t="s">
+      <c r="F55" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15652,7 +15640,7 @@
       <c r="B56" s="1" t="s">
         <v>1280</v>
       </c>
-      <c r="F56" s="0" t="s">
+      <c r="F56" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15663,7 +15651,7 @@
       <c r="B57" s="1" t="s">
         <v>1282</v>
       </c>
-      <c r="F57" s="0" t="s">
+      <c r="F57" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15674,7 +15662,7 @@
       <c r="B58" s="1" t="s">
         <v>1284</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="F58" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15685,7 +15673,7 @@
       <c r="B59" s="1" t="s">
         <v>1286</v>
       </c>
-      <c r="F59" s="0" t="s">
+      <c r="F59" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15696,7 +15684,7 @@
       <c r="B60" s="1" t="s">
         <v>1288</v>
       </c>
-      <c r="F60" s="0" t="s">
+      <c r="F60" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15707,7 +15695,7 @@
       <c r="B61" s="1" t="s">
         <v>1290</v>
       </c>
-      <c r="F61" s="0" t="s">
+      <c r="F61" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15718,7 +15706,7 @@
       <c r="B62" s="1" t="s">
         <v>1292</v>
       </c>
-      <c r="F62" s="0" t="s">
+      <c r="F62" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15729,7 +15717,7 @@
       <c r="B63" s="1" t="s">
         <v>1294</v>
       </c>
-      <c r="F63" s="0" t="s">
+      <c r="F63" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15740,7 +15728,7 @@
       <c r="B64" s="1" t="s">
         <v>1296</v>
       </c>
-      <c r="F64" s="0" t="s">
+      <c r="F64" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15751,7 +15739,7 @@
       <c r="B65" s="1" t="s">
         <v>1298</v>
       </c>
-      <c r="F65" s="0" t="s">
+      <c r="F65" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15770,7 +15758,7 @@
       <c r="B67" s="1" t="s">
         <v>1302</v>
       </c>
-      <c r="F67" s="0" t="s">
+      <c r="F67" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15781,7 +15769,7 @@
       <c r="B68" s="1" t="s">
         <v>1304</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="F68" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15792,7 +15780,7 @@
       <c r="B69" s="1" t="s">
         <v>1306</v>
       </c>
-      <c r="F69" s="0" t="s">
+      <c r="F69" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15803,7 +15791,7 @@
       <c r="B70" s="1" t="s">
         <v>1308</v>
       </c>
-      <c r="F70" s="0" t="s">
+      <c r="F70" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15814,7 +15802,7 @@
       <c r="B71" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F71" s="0" t="s">
+      <c r="F71" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15825,7 +15813,7 @@
       <c r="B72" s="1" t="s">
         <v>1311</v>
       </c>
-      <c r="F72" s="0" t="s">
+      <c r="F72" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15836,7 +15824,7 @@
       <c r="B73" s="1" t="s">
         <v>1313</v>
       </c>
-      <c r="F73" s="0" t="s">
+      <c r="F73" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15847,7 +15835,7 @@
       <c r="B74" s="1" t="s">
         <v>1315</v>
       </c>
-      <c r="F74" s="0" t="s">
+      <c r="F74" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15858,7 +15846,7 @@
       <c r="B75" s="1" t="s">
         <v>1317</v>
       </c>
-      <c r="F75" s="0" t="s">
+      <c r="F75" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15869,7 +15857,7 @@
       <c r="B76" s="1" t="s">
         <v>1319</v>
       </c>
-      <c r="F76" s="0" t="s">
+      <c r="F76" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15880,7 +15868,7 @@
       <c r="B77" s="1" t="s">
         <v>1321</v>
       </c>
-      <c r="F77" s="0" t="s">
+      <c r="F77" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15891,7 +15879,7 @@
       <c r="B78" s="1" t="s">
         <v>1323</v>
       </c>
-      <c r="F78" s="0" t="s">
+      <c r="F78" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15902,7 +15890,7 @@
       <c r="B79" s="1" t="s">
         <v>1325</v>
       </c>
-      <c r="F79" s="0" t="s">
+      <c r="F79" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15913,7 +15901,7 @@
       <c r="B80" s="1" t="s">
         <v>1327</v>
       </c>
-      <c r="F80" s="0" t="s">
+      <c r="F80" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15924,7 +15912,7 @@
       <c r="B81" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="F81" s="0" t="s">
+      <c r="F81" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15935,7 +15923,7 @@
       <c r="B82" s="1" t="s">
         <v>1331</v>
       </c>
-      <c r="F82" s="0" t="s">
+      <c r="F82" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15954,7 +15942,7 @@
       <c r="B84" s="1" t="s">
         <v>1335</v>
       </c>
-      <c r="F84" s="0" t="s">
+      <c r="F84" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15965,7 +15953,7 @@
       <c r="B85" s="1" t="s">
         <v>1335</v>
       </c>
-      <c r="F85" s="0" t="s">
+      <c r="F85" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15976,7 +15964,7 @@
       <c r="B86" s="1" t="s">
         <v>1338</v>
       </c>
-      <c r="F86" s="0" t="s">
+      <c r="F86" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15987,7 +15975,7 @@
       <c r="B87" s="1" t="s">
         <v>1340</v>
       </c>
-      <c r="F87" s="0" t="s">
+      <c r="F87" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15998,7 +15986,7 @@
       <c r="B88" s="1" t="s">
         <v>1342</v>
       </c>
-      <c r="F88" s="0" t="s">
+      <c r="F88" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16009,7 +15997,7 @@
       <c r="B89" s="1" t="s">
         <v>1344</v>
       </c>
-      <c r="F89" s="0" t="s">
+      <c r="F89" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16020,7 +16008,7 @@
       <c r="B90" s="1" t="s">
         <v>1346</v>
       </c>
-      <c r="F90" s="0" t="s">
+      <c r="F90" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16031,7 +16019,7 @@
       <c r="B91" s="1" t="s">
         <v>1348</v>
       </c>
-      <c r="F91" s="0" t="s">
+      <c r="F91" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16042,7 +16030,7 @@
       <c r="B92" s="1" t="s">
         <v>1350</v>
       </c>
-      <c r="F92" s="0" t="s">
+      <c r="F92" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16053,7 +16041,7 @@
       <c r="B93" s="1" t="s">
         <v>1352</v>
       </c>
-      <c r="F93" s="0" t="s">
+      <c r="F93" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16064,7 +16052,7 @@
       <c r="B94" s="1" t="s">
         <v>1354</v>
       </c>
-      <c r="F94" s="0" t="s">
+      <c r="F94" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16075,7 +16063,7 @@
       <c r="B95" s="1" t="s">
         <v>1356</v>
       </c>
-      <c r="F95" s="0" t="s">
+      <c r="F95" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16086,7 +16074,7 @@
       <c r="B96" s="1" t="s">
         <v>1358</v>
       </c>
-      <c r="F96" s="0" t="s">
+      <c r="F96" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16097,7 +16085,7 @@
       <c r="B97" s="1" t="s">
         <v>1360</v>
       </c>
-      <c r="F97" s="0" t="s">
+      <c r="F97" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16108,7 +16096,7 @@
       <c r="B98" s="1" t="s">
         <v>1362</v>
       </c>
-      <c r="F98" s="0" t="s">
+      <c r="F98" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16143,9 +16131,7 @@
       <c r="B1" s="1" t="s">
         <v>1364</v>
       </c>
-      <c r="F1" s="0" t="s">
-        <v>4</v>
-      </c>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -16154,7 +16140,7 @@
       <c r="B2" s="1" t="s">
         <v>1366</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16165,7 +16151,7 @@
       <c r="B3" s="1" t="s">
         <v>1368</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16176,7 +16162,7 @@
       <c r="B4" s="1" t="s">
         <v>1370</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16187,7 +16173,7 @@
       <c r="B5" s="1" t="s">
         <v>1372</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16198,7 +16184,7 @@
       <c r="B6" s="1" t="s">
         <v>1374</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16209,7 +16195,7 @@
       <c r="B7" s="1" t="s">
         <v>1376</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16220,7 +16206,7 @@
       <c r="B8" s="1" t="s">
         <v>1378</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16231,7 +16217,7 @@
       <c r="B9" s="1" t="s">
         <v>1380</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16242,7 +16228,7 @@
       <c r="B10" s="1" t="s">
         <v>1382</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16253,7 +16239,7 @@
       <c r="B11" s="1" t="s">
         <v>1384</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16264,7 +16250,7 @@
       <c r="B12" s="1" t="s">
         <v>1386</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16275,7 +16261,7 @@
       <c r="B13" s="1" t="s">
         <v>1388</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16286,7 +16272,7 @@
       <c r="B14" s="1" t="s">
         <v>1390</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16305,7 +16291,7 @@
       <c r="B16" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16316,7 +16302,7 @@
       <c r="B17" s="1" t="s">
         <v>1394</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16327,7 +16313,7 @@
       <c r="B18" s="1" t="s">
         <v>1396</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16338,7 +16324,7 @@
       <c r="B19" s="1" t="s">
         <v>1398</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16349,7 +16335,7 @@
       <c r="B20" s="1" t="s">
         <v>1400</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16360,7 +16346,7 @@
       <c r="B21" s="1" t="s">
         <v>1402</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16371,7 +16357,7 @@
       <c r="B22" s="1" t="s">
         <v>1404</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16382,7 +16368,7 @@
       <c r="B23" s="1" t="s">
         <v>1406</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16393,7 +16379,7 @@
       <c r="B24" s="1" t="s">
         <v>1408</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16404,7 +16390,7 @@
       <c r="B25" s="1" t="s">
         <v>1410</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16415,7 +16401,7 @@
       <c r="B26" s="1" t="s">
         <v>1412</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16426,7 +16412,7 @@
       <c r="B27" s="1" t="s">
         <v>1414</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16437,7 +16423,7 @@
       <c r="B28" s="1" t="s">
         <v>1416</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16448,7 +16434,7 @@
       <c r="B29" s="1" t="s">
         <v>1418</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16459,7 +16445,7 @@
       <c r="B30" s="1" t="s">
         <v>1420</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16470,7 +16456,7 @@
       <c r="B31" s="1" t="s">
         <v>1422</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16481,7 +16467,7 @@
       <c r="B32" s="1" t="s">
         <v>1424</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16492,7 +16478,7 @@
       <c r="B33" s="1" t="s">
         <v>1426</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="F33" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16503,7 +16489,7 @@
       <c r="B34" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16522,7 +16508,7 @@
       <c r="B36" s="1" t="s">
         <v>1432</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16533,7 +16519,7 @@
       <c r="B37" s="1" t="s">
         <v>1434</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16544,7 +16530,7 @@
       <c r="B38" s="1" t="s">
         <v>1436</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16555,7 +16541,7 @@
       <c r="B39" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16566,7 +16552,7 @@
       <c r="B40" s="1" t="s">
         <v>1440</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16577,7 +16563,7 @@
       <c r="B41" s="1" t="s">
         <v>1442</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16588,7 +16574,7 @@
       <c r="B42" s="1" t="s">
         <v>1444</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16599,7 +16585,7 @@
       <c r="B43" s="1" t="s">
         <v>1446</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="F43" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16610,7 +16596,7 @@
       <c r="B44" s="1" t="s">
         <v>1448</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16621,7 +16607,7 @@
       <c r="B45" s="1" t="s">
         <v>1450</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16632,7 +16618,7 @@
       <c r="B46" s="1" t="s">
         <v>1452</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16643,7 +16629,7 @@
       <c r="B47" s="1" t="s">
         <v>1454</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="F47" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16654,7 +16640,7 @@
       <c r="B48" s="1" t="s">
         <v>1456</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16673,7 +16659,7 @@
       <c r="B50" s="1" t="s">
         <v>1460</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16684,7 +16670,7 @@
       <c r="B51" s="1" t="s">
         <v>1462</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16695,7 +16681,7 @@
       <c r="B52" s="1" t="s">
         <v>1464</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="F52" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16706,7 +16692,7 @@
       <c r="B53" s="1" t="s">
         <v>1466</v>
       </c>
-      <c r="F53" s="0" t="s">
+      <c r="F53" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16717,7 +16703,7 @@
       <c r="B54" s="1" t="s">
         <v>1468</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="F54" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16728,7 +16714,7 @@
       <c r="B55" s="1" t="s">
         <v>1470</v>
       </c>
-      <c r="F55" s="0" t="s">
+      <c r="F55" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16739,7 +16725,7 @@
       <c r="B56" s="1" t="s">
         <v>1472</v>
       </c>
-      <c r="F56" s="0" t="s">
+      <c r="F56" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16750,7 +16736,7 @@
       <c r="B57" s="1" t="s">
         <v>1474</v>
       </c>
-      <c r="F57" s="0" t="s">
+      <c r="F57" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16761,7 +16747,7 @@
       <c r="B58" s="1" t="s">
         <v>1476</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="F58" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16772,7 +16758,7 @@
       <c r="B59" s="1" t="s">
         <v>1478</v>
       </c>
-      <c r="F59" s="0" t="s">
+      <c r="F59" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16783,7 +16769,7 @@
       <c r="B60" s="1" t="s">
         <v>1480</v>
       </c>
-      <c r="F60" s="0" t="s">
+      <c r="F60" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16794,7 +16780,7 @@
       <c r="B61" s="1" t="s">
         <v>1482</v>
       </c>
-      <c r="F61" s="0" t="s">
+      <c r="F61" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16805,7 +16791,7 @@
       <c r="B62" s="1" t="s">
         <v>1484</v>
       </c>
-      <c r="F62" s="0" t="s">
+      <c r="F62" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16816,7 +16802,7 @@
       <c r="B63" s="1" t="s">
         <v>1486</v>
       </c>
-      <c r="F63" s="0" t="s">
+      <c r="F63" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16827,7 +16813,7 @@
       <c r="B64" s="1" t="s">
         <v>1488</v>
       </c>
-      <c r="F64" s="0" t="s">
+      <c r="F64" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16838,7 +16824,7 @@
       <c r="B65" s="1" t="s">
         <v>1490</v>
       </c>
-      <c r="F65" s="0" t="s">
+      <c r="F65" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16849,7 +16835,7 @@
       <c r="B66" s="1" t="s">
         <v>1492</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="F66" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16860,7 +16846,7 @@
       <c r="B67" s="1" t="s">
         <v>1494</v>
       </c>
-      <c r="F67" s="0" t="s">
+      <c r="F67" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16871,7 +16857,7 @@
       <c r="B68" s="1" t="s">
         <v>1496</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="F68" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16882,7 +16868,7 @@
       <c r="B69" s="1" t="s">
         <v>1498</v>
       </c>
-      <c r="F69" s="0" t="s">
+      <c r="F69" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16893,7 +16879,7 @@
       <c r="B70" s="1" t="s">
         <v>1500</v>
       </c>
-      <c r="F70" s="0" t="s">
+      <c r="F70" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16904,7 +16890,7 @@
       <c r="B71" s="1" t="s">
         <v>1502</v>
       </c>
-      <c r="F71" s="0" t="s">
+      <c r="F71" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16915,7 +16901,7 @@
       <c r="B72" s="1" t="s">
         <v>1504</v>
       </c>
-      <c r="F72" s="0" t="s">
+      <c r="F72" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16926,7 +16912,7 @@
       <c r="B73" s="1" t="s">
         <v>1506</v>
       </c>
-      <c r="F73" s="0" t="s">
+      <c r="F73" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16937,7 +16923,7 @@
       <c r="B74" s="1" t="s">
         <v>1508</v>
       </c>
-      <c r="F74" s="0" t="s">
+      <c r="F74" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16948,7 +16934,7 @@
       <c r="B75" s="1" t="s">
         <v>1510</v>
       </c>
-      <c r="F75" s="0" t="s">
+      <c r="F75" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16959,7 +16945,7 @@
       <c r="B76" s="1" t="s">
         <v>1512</v>
       </c>
-      <c r="F76" s="0" t="s">
+      <c r="F76" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16970,7 +16956,7 @@
       <c r="B77" s="1" t="s">
         <v>1514</v>
       </c>
-      <c r="F77" s="0" t="s">
+      <c r="F77" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -16981,7 +16967,7 @@
       <c r="B78" s="1" t="s">
         <v>1516</v>
       </c>
-      <c r="F78" s="0" t="s">
+      <c r="F78" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17000,7 +16986,7 @@
       <c r="B80" s="1" t="s">
         <v>1520</v>
       </c>
-      <c r="F80" s="0" t="s">
+      <c r="F80" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17011,7 +16997,7 @@
       <c r="B81" s="1" t="s">
         <v>1522</v>
       </c>
-      <c r="F81" s="0" t="s">
+      <c r="F81" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17022,7 +17008,7 @@
       <c r="B82" s="1" t="s">
         <v>1524</v>
       </c>
-      <c r="F82" s="0" t="s">
+      <c r="F82" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17033,7 +17019,7 @@
       <c r="B83" s="1" t="s">
         <v>1526</v>
       </c>
-      <c r="F83" s="0" t="s">
+      <c r="F83" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17044,7 +17030,7 @@
       <c r="B84" s="1" t="s">
         <v>1528</v>
       </c>
-      <c r="F84" s="0" t="s">
+      <c r="F84" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17055,7 +17041,7 @@
       <c r="B85" s="1" t="s">
         <v>1530</v>
       </c>
-      <c r="F85" s="0" t="s">
+      <c r="F85" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17066,7 +17052,7 @@
       <c r="B86" s="1" t="s">
         <v>1532</v>
       </c>
-      <c r="F86" s="0" t="s">
+      <c r="F86" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17077,7 +17063,7 @@
       <c r="B87" s="1" t="s">
         <v>1534</v>
       </c>
-      <c r="F87" s="0" t="s">
+      <c r="F87" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17088,7 +17074,7 @@
       <c r="B88" s="1" t="s">
         <v>1536</v>
       </c>
-      <c r="F88" s="0" t="s">
+      <c r="F88" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17099,7 +17085,7 @@
       <c r="B89" s="1" t="s">
         <v>1538</v>
       </c>
-      <c r="F89" s="0" t="s">
+      <c r="F89" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17110,7 +17096,7 @@
       <c r="B90" s="1" t="s">
         <v>1540</v>
       </c>
-      <c r="F90" s="0" t="s">
+      <c r="F90" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17121,7 +17107,7 @@
       <c r="B91" s="1" t="s">
         <v>1542</v>
       </c>
-      <c r="F91" s="0" t="s">
+      <c r="F91" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17132,7 +17118,7 @@
       <c r="B92" s="1" t="s">
         <v>1544</v>
       </c>
-      <c r="F92" s="0" t="s">
+      <c r="F92" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17143,7 +17129,7 @@
       <c r="B93" s="1" t="s">
         <v>1546</v>
       </c>
-      <c r="F93" s="0" t="s">
+      <c r="F93" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17154,7 +17140,7 @@
       <c r="B94" s="1" t="s">
         <v>1548</v>
       </c>
-      <c r="F94" s="0" t="s">
+      <c r="F94" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17165,7 +17151,7 @@
       <c r="B95" s="1" t="s">
         <v>1550</v>
       </c>
-      <c r="F95" s="0" t="s">
+      <c r="F95" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17176,7 +17162,7 @@
       <c r="B96" s="1" t="s">
         <v>1552</v>
       </c>
-      <c r="F96" s="0" t="s">
+      <c r="F96" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17211,9 +17197,7 @@
       <c r="B1" s="1" t="s">
         <v>1554</v>
       </c>
-      <c r="F1" s="0" t="s">
-        <v>4</v>
-      </c>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -17222,7 +17206,7 @@
       <c r="B2" s="1" t="s">
         <v>1556</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17233,7 +17217,7 @@
       <c r="B3" s="1" t="s">
         <v>1558</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17244,7 +17228,7 @@
       <c r="B4" s="1" t="s">
         <v>1050</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17255,7 +17239,7 @@
       <c r="B5" s="1" t="s">
         <v>1561</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17266,7 +17250,7 @@
       <c r="B6" s="1" t="s">
         <v>1048</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17277,7 +17261,7 @@
       <c r="B7" s="1" t="s">
         <v>1563</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17288,7 +17272,7 @@
       <c r="B8" s="1" t="s">
         <v>1565</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17299,7 +17283,7 @@
       <c r="B9" s="1" t="s">
         <v>1567</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17310,7 +17294,7 @@
       <c r="B10" s="1" t="s">
         <v>1569</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17321,7 +17305,7 @@
       <c r="B11" s="1" t="s">
         <v>1571</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17332,7 +17316,7 @@
       <c r="B12" s="1" t="s">
         <v>1573</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17343,7 +17327,7 @@
       <c r="B13" s="1" t="s">
         <v>1575</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17354,7 +17338,7 @@
       <c r="B14" s="1" t="s">
         <v>1577</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17365,7 +17349,7 @@
       <c r="B15" s="1" t="s">
         <v>1579</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17376,7 +17360,7 @@
       <c r="B16" s="1" t="s">
         <v>1581</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17387,7 +17371,7 @@
       <c r="B17" s="1" t="s">
         <v>1583</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17398,7 +17382,7 @@
       <c r="B18" s="1" t="s">
         <v>1585</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17409,7 +17393,7 @@
       <c r="B19" s="1" t="s">
         <v>1587</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17420,7 +17404,7 @@
       <c r="B20" s="1" t="s">
         <v>1589</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17431,7 +17415,7 @@
       <c r="B21" s="1" t="s">
         <v>1591</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17442,7 +17426,7 @@
       <c r="B22" s="1" t="s">
         <v>1593</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17453,7 +17437,7 @@
       <c r="B23" s="1" t="s">
         <v>1054</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17464,7 +17448,7 @@
       <c r="B24" s="1" t="s">
         <v>1595</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17475,7 +17459,7 @@
       <c r="B25" s="1" t="s">
         <v>1597</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17486,7 +17470,7 @@
       <c r="B26" s="1" t="s">
         <v>1599</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17497,7 +17481,7 @@
       <c r="B27" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17508,7 +17492,7 @@
       <c r="B28" s="1" t="s">
         <v>1601</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17519,7 +17503,7 @@
       <c r="B29" s="1" t="s">
         <v>1603</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17530,7 +17514,7 @@
       <c r="B30" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17541,7 +17525,7 @@
       <c r="B31" s="1" t="s">
         <v>1605</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17552,7 +17536,7 @@
       <c r="B32" s="1" t="s">
         <v>1607</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17571,7 +17555,7 @@
       <c r="B34" s="1" t="s">
         <v>1611</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17582,7 +17566,7 @@
       <c r="B35" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17593,7 +17577,7 @@
       <c r="B36" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17604,7 +17588,7 @@
       <c r="B37" s="1" t="s">
         <v>1614</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17615,7 +17599,7 @@
       <c r="B38" s="1" t="s">
         <v>1616</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17626,7 +17610,7 @@
       <c r="B39" s="1" t="s">
         <v>1618</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17637,7 +17621,7 @@
       <c r="B40" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17648,7 +17632,7 @@
       <c r="B41" s="1" t="s">
         <v>1621</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17659,7 +17643,7 @@
       <c r="B42" s="1" t="s">
         <v>1623</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17670,7 +17654,7 @@
       <c r="B43" s="1" t="s">
         <v>1625</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="F43" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17681,7 +17665,7 @@
       <c r="B44" s="1" t="s">
         <v>1627</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17692,7 +17676,7 @@
       <c r="B45" s="1" t="s">
         <v>1629</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17703,7 +17687,7 @@
       <c r="B46" s="1" t="s">
         <v>1631</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17714,7 +17698,7 @@
       <c r="B47" s="1" t="s">
         <v>1633</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="F47" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17725,7 +17709,7 @@
       <c r="B48" s="1" t="s">
         <v>1635</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17736,7 +17720,7 @@
       <c r="B49" s="1" t="s">
         <v>1637</v>
       </c>
-      <c r="F49" s="0" t="s">
+      <c r="F49" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17755,7 +17739,7 @@
       <c r="B51" s="1" t="s">
         <v>1641</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17766,7 +17750,7 @@
       <c r="B52" s="1" t="s">
         <v>1643</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="F52" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17777,7 +17761,7 @@
       <c r="B53" s="1" t="s">
         <v>1645</v>
       </c>
-      <c r="F53" s="0" t="s">
+      <c r="F53" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17788,7 +17772,7 @@
       <c r="B54" s="1" t="s">
         <v>1647</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="F54" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17799,7 +17783,7 @@
       <c r="B55" s="1" t="s">
         <v>1649</v>
       </c>
-      <c r="F55" s="0" t="s">
+      <c r="F55" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17810,7 +17794,7 @@
       <c r="B56" s="1" t="s">
         <v>1651</v>
       </c>
-      <c r="F56" s="0" t="s">
+      <c r="F56" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17821,7 +17805,7 @@
       <c r="B57" s="1" t="s">
         <v>1653</v>
       </c>
-      <c r="F57" s="0" t="s">
+      <c r="F57" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17832,7 +17816,7 @@
       <c r="B58" s="1" t="s">
         <v>1655</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="F58" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17843,7 +17827,7 @@
       <c r="B59" s="1" t="s">
         <v>1657</v>
       </c>
-      <c r="F59" s="0" t="s">
+      <c r="F59" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17854,7 +17838,7 @@
       <c r="B60" s="1" t="s">
         <v>1659</v>
       </c>
-      <c r="F60" s="0" t="s">
+      <c r="F60" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17865,7 +17849,7 @@
       <c r="B61" s="1" t="s">
         <v>1661</v>
       </c>
-      <c r="F61" s="0" t="s">
+      <c r="F61" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17876,7 +17860,7 @@
       <c r="B62" s="1" t="s">
         <v>1663</v>
       </c>
-      <c r="F62" s="0" t="s">
+      <c r="F62" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17887,7 +17871,7 @@
       <c r="B63" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="F63" s="0" t="s">
+      <c r="F63" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17898,7 +17882,7 @@
       <c r="B64" s="1" t="s">
         <v>1666</v>
       </c>
-      <c r="F64" s="0" t="s">
+      <c r="F64" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17909,7 +17893,7 @@
       <c r="B65" s="1" t="s">
         <v>1668</v>
       </c>
-      <c r="F65" s="0" t="s">
+      <c r="F65" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17920,7 +17904,7 @@
       <c r="B66" s="1" t="s">
         <v>1670</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="F66" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17931,7 +17915,7 @@
       <c r="B67" s="1" t="s">
         <v>1672</v>
       </c>
-      <c r="F67" s="0" t="s">
+      <c r="F67" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17942,7 +17926,7 @@
       <c r="B68" s="1" t="s">
         <v>1674</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="F68" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17953,7 +17937,7 @@
       <c r="B69" s="1" t="s">
         <v>1676</v>
       </c>
-      <c r="F69" s="0" t="s">
+      <c r="F69" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17964,7 +17948,7 @@
       <c r="B70" s="1" t="s">
         <v>1678</v>
       </c>
-      <c r="F70" s="0" t="s">
+      <c r="F70" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17983,7 +17967,7 @@
       <c r="B72" s="1" t="s">
         <v>1682</v>
       </c>
-      <c r="F72" s="0" t="s">
+      <c r="F72" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17994,7 +17978,7 @@
       <c r="B73" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="F73" s="0" t="s">
+      <c r="F73" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18005,7 +17989,7 @@
       <c r="B74" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="F74" s="0" t="s">
+      <c r="F74" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18016,7 +18000,7 @@
       <c r="B75" s="1" t="s">
         <v>1685</v>
       </c>
-      <c r="F75" s="0" t="s">
+      <c r="F75" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18027,7 +18011,7 @@
       <c r="B76" s="1" t="s">
         <v>1687</v>
       </c>
-      <c r="F76" s="0" t="s">
+      <c r="F76" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18038,7 +18022,7 @@
       <c r="B77" s="1" t="s">
         <v>1689</v>
       </c>
-      <c r="F77" s="0" t="s">
+      <c r="F77" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18049,7 +18033,7 @@
       <c r="B78" s="1" t="s">
         <v>1691</v>
       </c>
-      <c r="F78" s="0" t="s">
+      <c r="F78" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18060,7 +18044,7 @@
       <c r="B79" s="1" t="s">
         <v>1693</v>
       </c>
-      <c r="F79" s="0" t="s">
+      <c r="F79" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18071,7 +18055,7 @@
       <c r="B80" s="1" t="s">
         <v>1695</v>
       </c>
-      <c r="F80" s="0" t="s">
+      <c r="F80" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18082,7 +18066,7 @@
       <c r="B81" s="1" t="s">
         <v>1697</v>
       </c>
-      <c r="F81" s="0" t="s">
+      <c r="F81" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18093,7 +18077,7 @@
       <c r="B82" s="1" t="s">
         <v>1699</v>
       </c>
-      <c r="F82" s="0" t="s">
+      <c r="F82" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18104,7 +18088,7 @@
       <c r="B83" s="1" t="s">
         <v>1701</v>
       </c>
-      <c r="F83" s="0" t="s">
+      <c r="F83" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18115,7 +18099,7 @@
       <c r="B84" s="1" t="s">
         <v>1703</v>
       </c>
-      <c r="F84" s="0" t="s">
+      <c r="F84" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18126,7 +18110,7 @@
       <c r="B85" s="1" t="s">
         <v>1705</v>
       </c>
-      <c r="F85" s="0" t="s">
+      <c r="F85" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18137,7 +18121,7 @@
       <c r="B86" s="1" t="s">
         <v>1707</v>
       </c>
-      <c r="F86" s="0" t="s">
+      <c r="F86" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18148,7 +18132,7 @@
       <c r="B87" s="1" t="s">
         <v>1709</v>
       </c>
-      <c r="F87" s="0" t="s">
+      <c r="F87" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18159,7 +18143,7 @@
       <c r="B88" s="1" t="s">
         <v>1711</v>
       </c>
-      <c r="F88" s="0" t="s">
+      <c r="F88" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18170,7 +18154,7 @@
       <c r="B89" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F89" s="0" t="s">
+      <c r="F89" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18181,7 +18165,7 @@
       <c r="B90" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="F90" s="0" t="s">
+      <c r="F90" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18192,7 +18176,7 @@
       <c r="B91" s="1" t="s">
         <v>1714</v>
       </c>
-      <c r="F91" s="0" t="s">
+      <c r="F91" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18203,7 +18187,7 @@
       <c r="B92" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="F92" s="0" t="s">
+      <c r="F92" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18214,7 +18198,7 @@
       <c r="B93" s="1" t="s">
         <v>1716</v>
       </c>
-      <c r="F93" s="0" t="s">
+      <c r="F93" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18225,7 +18209,7 @@
       <c r="B94" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="F94" s="0" t="s">
+      <c r="F94" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18236,7 +18220,7 @@
       <c r="B95" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="F95" s="0" t="s">
+      <c r="F95" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18247,7 +18231,7 @@
       <c r="B96" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="F96" s="0" t="s">
+      <c r="F96" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18258,7 +18242,7 @@
       <c r="B97" s="1" t="s">
         <v>1718</v>
       </c>
-      <c r="F97" s="0" t="s">
+      <c r="F97" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18277,7 +18261,7 @@
       <c r="B99" s="1" t="s">
         <v>1722</v>
       </c>
-      <c r="F99" s="0" t="s">
+      <c r="F99" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18288,7 +18272,7 @@
       <c r="B100" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F100" s="0" t="s">
+      <c r="F100" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18299,7 +18283,7 @@
       <c r="B101" s="1" t="s">
         <v>1724</v>
       </c>
-      <c r="F101" s="0" t="s">
+      <c r="F101" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18310,7 +18294,7 @@
       <c r="B102" s="1" t="s">
         <v>1726</v>
       </c>
-      <c r="F102" s="0" t="s">
+      <c r="F102" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18321,7 +18305,7 @@
       <c r="B103" s="1" t="s">
         <v>1728</v>
       </c>
-      <c r="F103" s="0" t="s">
+      <c r="F103" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18332,7 +18316,7 @@
       <c r="B104" s="1" t="s">
         <v>1730</v>
       </c>
-      <c r="F104" s="0" t="s">
+      <c r="F104" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18343,7 +18327,7 @@
       <c r="B105" s="1" t="s">
         <v>1732</v>
       </c>
-      <c r="F105" s="0" t="s">
+      <c r="F105" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18354,7 +18338,7 @@
       <c r="B106" s="1" t="s">
         <v>1734</v>
       </c>
-      <c r="F106" s="0" t="s">
+      <c r="F106" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18365,7 +18349,7 @@
       <c r="B107" s="1" t="s">
         <v>1736</v>
       </c>
-      <c r="F107" s="0" t="s">
+      <c r="F107" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18376,7 +18360,7 @@
       <c r="B108" s="1" t="s">
         <v>1738</v>
       </c>
-      <c r="F108" s="0" t="s">
+      <c r="F108" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18387,7 +18371,7 @@
       <c r="B109" s="1" t="s">
         <v>1740</v>
       </c>
-      <c r="F109" s="0" t="s">
+      <c r="F109" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18398,7 +18382,7 @@
       <c r="B110" s="1" t="s">
         <v>1742</v>
       </c>
-      <c r="F110" s="0" t="s">
+      <c r="F110" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18409,7 +18393,7 @@
       <c r="B111" s="1" t="s">
         <v>1744</v>
       </c>
-      <c r="F111" s="0" t="s">
+      <c r="F111" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -18420,7 +18404,7 @@
       <c r="B112" s="1" t="s">
         <v>1746</v>
       </c>
-      <c r="F112" s="0" t="s">
+      <c r="F112" s="1" t="s">
         <v>4</v>
       </c>
     </row>

--- a/src/main/resources/espacios/0 Step/0 - Basic Sentence.xlsx
+++ b/src/main/resources/espacios/0 Step/0 - Basic Sentence.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3142" uniqueCount="2027">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3162" uniqueCount="2027">
   <si>
     <t xml:space="preserve">talking about time</t>
   </si>
@@ -6382,12 +6382,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6816,6 +6820,9 @@
       <c r="B20" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="F20" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
@@ -7249,6 +7256,9 @@
       </c>
       <c r="B60" s="1" t="s">
         <v>116</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7816,6 +7826,9 @@
       <c r="B22" s="1" t="s">
         <v>1790</v>
       </c>
+      <c r="F22" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
@@ -7978,6 +7991,9 @@
       <c r="B37" s="1" t="s">
         <v>1816</v>
       </c>
+      <c r="F37" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
@@ -8008,9 +8024,7 @@
       <c r="B40" s="1" t="s">
         <v>1822</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
@@ -8161,6 +8175,9 @@
       </c>
       <c r="B54" s="1" t="s">
         <v>1850</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8467,6 +8484,9 @@
       <c r="B11" s="1" t="s">
         <v>1900</v>
       </c>
+      <c r="F11" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
@@ -8629,6 +8649,9 @@
       <c r="B26" s="1" t="s">
         <v>1930</v>
       </c>
+      <c r="F26" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
@@ -8780,9 +8803,7 @@
       <c r="B40" s="1" t="s">
         <v>1958</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
@@ -8911,6 +8932,9 @@
       </c>
       <c r="B52" s="1" t="s">
         <v>1982</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9481,6 +9505,9 @@
       <c r="B28" s="1" t="s">
         <v>225</v>
       </c>
+      <c r="F28" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
@@ -9610,9 +9637,7 @@
       <c r="B40" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
@@ -9709,6 +9734,9 @@
       <c r="B49" s="1" t="s">
         <v>258</v>
       </c>
+      <c r="F49" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
@@ -9992,6 +10020,9 @@
       <c r="B75" s="1" t="s">
         <v>304</v>
       </c>
+      <c r="F75" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
@@ -10044,9 +10075,7 @@
       <c r="B80" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F80" s="1"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
@@ -10583,6 +10612,9 @@
       <c r="B32" s="1" t="s">
         <v>402</v>
       </c>
+      <c r="F32" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
@@ -10668,9 +10700,7 @@
       <c r="B40" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
@@ -10833,6 +10863,9 @@
       <c r="B55" s="1" t="s">
         <v>446</v>
       </c>
+      <c r="F55" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
@@ -11105,9 +11138,7 @@
       <c r="B80" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F80" s="1"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
@@ -11115,6 +11146,9 @@
       </c>
       <c r="B81" s="1" t="s">
         <v>496</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11574,7 +11608,7 @@
     <tabColor rgb="FF00A933"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="56.88"/>
@@ -11905,6 +11939,9 @@
       <c r="B30" s="1" t="s">
         <v>631</v>
       </c>
+      <c r="F30" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
@@ -12012,9 +12049,7 @@
       <c r="B40" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
@@ -12221,6 +12256,9 @@
       <c r="B59" s="1" t="s">
         <v>687</v>
       </c>
+      <c r="F59" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
@@ -12449,9 +12487,7 @@
       <c r="B80" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F80" s="1"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
@@ -12498,16 +12534,22 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>737</v>
+      </c>
       <c r="F85" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>4</v>
@@ -12515,10 +12557,10 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>4</v>
@@ -12526,10 +12568,10 @@
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>4</v>
@@ -12537,10 +12579,10 @@
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>4</v>
@@ -12548,10 +12590,10 @@
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>4</v>
@@ -12559,10 +12601,10 @@
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>4</v>
@@ -12570,10 +12612,10 @@
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>4</v>
@@ -12581,10 +12623,10 @@
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>4</v>
@@ -12592,10 +12634,10 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>752</v>
+        <v>552</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>753</v>
+        <v>553</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>4</v>
@@ -12603,10 +12645,10 @@
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>552</v>
+        <v>754</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>553</v>
+        <v>755</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>4</v>
@@ -12614,10 +12656,10 @@
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>4</v>
@@ -12625,10 +12667,10 @@
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>4</v>
@@ -12636,10 +12678,10 @@
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>4</v>
@@ -12647,10 +12689,10 @@
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>4</v>
@@ -12658,10 +12700,10 @@
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>4</v>
@@ -12669,10 +12711,10 @@
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>4</v>
@@ -12680,10 +12722,10 @@
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>4</v>
@@ -12691,10 +12733,10 @@
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>4</v>
@@ -12702,10 +12744,10 @@
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>4</v>
@@ -12713,10 +12755,10 @@
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>4</v>
@@ -12724,10 +12766,10 @@
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>4</v>
@@ -12735,10 +12777,10 @@
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>4</v>
@@ -12746,10 +12788,10 @@
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>4</v>
@@ -12757,10 +12799,10 @@
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>4</v>
@@ -12768,10 +12810,10 @@
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>4</v>
@@ -12779,10 +12821,10 @@
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>4</v>
@@ -12790,10 +12832,10 @@
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>787</v>
+        <v>197</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>4</v>
@@ -12801,10 +12843,10 @@
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>197</v>
+        <v>790</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>4</v>
@@ -12812,10 +12854,10 @@
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>4</v>
@@ -12823,10 +12865,10 @@
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>4</v>
@@ -12834,10 +12876,10 @@
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>4</v>
@@ -12845,10 +12887,10 @@
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>4</v>
@@ -12856,10 +12898,10 @@
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>4</v>
@@ -12867,23 +12909,12 @@
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>802</v>
-      </c>
-      <c r="F120" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12912,7 +12943,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>803</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -13213,6 +13244,9 @@
       <c r="B28" s="1" t="s">
         <v>856</v>
       </c>
+      <c r="F28" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
@@ -13342,9 +13376,7 @@
       <c r="B40" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
@@ -13441,6 +13473,9 @@
       <c r="B49" s="1" t="s">
         <v>894</v>
       </c>
+      <c r="F49" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
@@ -13570,6 +13605,9 @@
       <c r="B61" s="1" t="s">
         <v>918</v>
       </c>
+      <c r="F61" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
@@ -13698,6 +13736,9 @@
       </c>
       <c r="B73" s="1" t="s">
         <v>940</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13916,6 +13957,9 @@
       <c r="B13" s="1" t="s">
         <v>976</v>
       </c>
+      <c r="F13" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
@@ -14166,6 +14210,9 @@
       <c r="B36" s="1" t="s">
         <v>1022</v>
       </c>
+      <c r="F36" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
@@ -14207,9 +14254,7 @@
       <c r="B40" s="1" t="s">
         <v>1030</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
@@ -14383,6 +14428,9 @@
       <c r="B56" s="1" t="s">
         <v>1060</v>
       </c>
+      <c r="F56" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
@@ -14534,6 +14582,9 @@
       <c r="B70" s="1" t="s">
         <v>1088</v>
       </c>
+      <c r="F70" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
@@ -14641,9 +14692,7 @@
       <c r="B80" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F80" s="1"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
@@ -14696,6 +14745,9 @@
       <c r="B85" s="1" t="s">
         <v>1117</v>
       </c>
+      <c r="F85" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
@@ -14846,6 +14898,9 @@
       </c>
       <c r="B99" s="1" t="s">
         <v>1143</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15217,6 +15272,9 @@
       <c r="B17" s="1" t="s">
         <v>1207</v>
       </c>
+      <c r="F17" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
@@ -15445,6 +15503,9 @@
       <c r="B38" s="1" t="s">
         <v>1244</v>
       </c>
+      <c r="F38" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
@@ -15464,9 +15525,7 @@
       <c r="B40" s="1" t="s">
         <v>1248</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
@@ -15750,6 +15809,9 @@
       <c r="B66" s="1" t="s">
         <v>1300</v>
       </c>
+      <c r="F66" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
@@ -15901,9 +15963,7 @@
       <c r="B80" s="1" t="s">
         <v>1327</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F80" s="1"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
@@ -15933,6 +15993,9 @@
       </c>
       <c r="B83" s="1" t="s">
         <v>1333</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16283,6 +16346,9 @@
       <c r="B15" s="1" t="s">
         <v>1392</v>
       </c>
+      <c r="F15" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
@@ -16500,6 +16566,9 @@
       <c r="B35" s="1" t="s">
         <v>1430</v>
       </c>
+      <c r="F35" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
@@ -16552,9 +16621,7 @@
       <c r="B40" s="1" t="s">
         <v>1440</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
@@ -16651,6 +16718,9 @@
       <c r="B49" s="1" t="s">
         <v>1458</v>
       </c>
+      <c r="F49" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
@@ -16978,6 +17048,9 @@
       <c r="B79" s="1" t="s">
         <v>1518</v>
       </c>
+      <c r="F79" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
@@ -16986,9 +17059,7 @@
       <c r="B80" s="1" t="s">
         <v>1520</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F80" s="1"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
@@ -17547,6 +17618,9 @@
       <c r="B33" s="1" t="s">
         <v>1609</v>
       </c>
+      <c r="F33" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
@@ -17621,9 +17695,7 @@
       <c r="B40" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
@@ -17731,6 +17803,9 @@
       <c r="B50" s="1" t="s">
         <v>1639</v>
       </c>
+      <c r="F50" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
@@ -17959,6 +18034,9 @@
       <c r="B71" s="1" t="s">
         <v>1680</v>
       </c>
+      <c r="F71" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
@@ -18055,9 +18133,7 @@
       <c r="B80" s="1" t="s">
         <v>1695</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F80" s="1"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
@@ -18252,6 +18328,9 @@
       </c>
       <c r="B98" s="1" t="s">
         <v>1720</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/src/main/resources/espacios/0 Step/0 - Basic Sentence.xlsx
+++ b/src/main/resources/espacios/0 Step/0 - Basic Sentence.xlsx
@@ -6387,15 +6387,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6605,6 +6605,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="47.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="60.02"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="3" style="2" width="11.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6820,7 +6821,7 @@
       <c r="B20" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7257,7 +7258,7 @@
       <c r="B60" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="F60" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7588,6 +7589,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="56.69"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="62.43"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="3" style="2" width="11.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8367,6 +8369,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="39.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="51.87"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="3" style="2" width="11.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9201,6 +9204,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="56.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="61.87"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="3" style="2" width="11.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9505,7 +9509,7 @@
       <c r="B28" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9734,7 +9738,7 @@
       <c r="B49" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10020,7 +10024,7 @@
       <c r="B75" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="F75" s="2" t="s">
+      <c r="F75" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10264,6 +10268,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="62.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="75.03"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="3" style="2" width="11.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10612,7 +10617,7 @@
       <c r="B32" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10863,7 +10868,7 @@
       <c r="B55" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F55" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -11614,6 +11619,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="56.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="61.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="46.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="2" width="11.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12940,10 +12946,11 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="61.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="62.43"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="3" style="2" width="11.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>803</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -13818,6 +13825,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="60.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="68.92"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="3" style="2" width="11.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15090,6 +15098,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="45.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52.42"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="3" style="2" width="11.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16185,6 +16194,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.61"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="3" style="2" width="11.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17259,6 +17269,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.23"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="3" style="2" width="11.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
